--- a/Capítulo05/GOMES PEREIRA.xlsx
+++ b/Capítulo05/GOMES PEREIRA.xlsx
@@ -1,33 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo05/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{14B14226-F974-43A2-9F36-8BB23CBE65E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC8333BC-811E-4F34-B451-988E9A929B5F}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="13_ncr:1_{14B14226-F974-43A2-9F36-8BB23CBE65E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7244862F-DB75-4E0C-A96D-0849879F7482}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CADASTRO" sheetId="1" r:id="rId1"/>
-    <sheet name="RELATÓRIO" sheetId="2" r:id="rId2"/>
-    <sheet name="CRITÉRIOS" sheetId="3" r:id="rId3"/>
-    <sheet name="Planilha1" sheetId="4" r:id="rId4"/>
+    <sheet name="Planilha2" sheetId="5" r:id="rId1"/>
+    <sheet name="TABdinamica" sheetId="6" r:id="rId2"/>
+    <sheet name="CADASTRO" sheetId="1" r:id="rId3"/>
+    <sheet name="RELATÓRIO" sheetId="2" r:id="rId4"/>
+    <sheet name="CRITÉRIOS" sheetId="3" r:id="rId5"/>
+    <sheet name="Planilha1" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CADASTRO!$A$2:$F$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CADASTRO!$A$2:$F$104</definedName>
     <definedName name="ADM">CRITÉRIOS!$A$1:$A$2</definedName>
+    <definedName name="adm_max_idd">CRITÉRIOS!$H$1:$I$2</definedName>
+    <definedName name="adm_max_sal">CRITÉRIOS!$A$1:$B$2</definedName>
+    <definedName name="adm_min_idd">CRITÉRIOS!$K$1:$L$2</definedName>
+    <definedName name="adm_min_sal">CRITÉRIOS!$D$1:$E$2</definedName>
+    <definedName name="analista">CRITÉRIOS!$A$10:$A$11</definedName>
+    <definedName name="assistente">CRITÉRIOS!$A$12:$A$13</definedName>
+    <definedName name="cargo">CADASTRO!$C$2</definedName>
     <definedName name="DADOS">CADASTRO!$A$2:$F$104</definedName>
     <definedName name="FIN">CRITÉRIOS!$A$3:$A$4</definedName>
+    <definedName name="fin_max_idd">CRITÉRIOS!$H$3:$I$4</definedName>
+    <definedName name="fin_max_sal">CRITÉRIOS!$A$3:$B$4</definedName>
+    <definedName name="fin_min_idd">CRITÉRIOS!$K$3:$L$4</definedName>
+    <definedName name="fin_min_sal">CRITÉRIOS!$D$3:$E$4</definedName>
+    <definedName name="funcionario">CADASTRO!$A$2</definedName>
+    <definedName name="gerente">CRITÉRIOS!$A$16:$A$17</definedName>
+    <definedName name="idade">CADASTRO!$F$2</definedName>
     <definedName name="INF">CRITÉRIOS!$A$5:$A$6</definedName>
+    <definedName name="inf_max_idd">CRITÉRIOS!$H$5:$I$6</definedName>
+    <definedName name="inf_max_sal">CRITÉRIOS!$A$5:$B$6</definedName>
+    <definedName name="inf_min_idd">CRITÉRIOS!$K$5:$L$6</definedName>
+    <definedName name="inf_min_sal">CRITÉRIOS!$D$5:$E$6</definedName>
     <definedName name="RH">CRITÉRIOS!$A$7:$A$8</definedName>
+    <definedName name="rh_max_idd">CRITÉRIOS!$H$7:$I$8</definedName>
+    <definedName name="rh_max_sal">CRITÉRIOS!$A$7:$B$8</definedName>
+    <definedName name="rh_min_idd">CRITÉRIOS!$K$7:$L$8</definedName>
+    <definedName name="rh_min_sal">CRITÉRIOS!$D$7:$E$8</definedName>
     <definedName name="salario">CADASTRO!$D$2</definedName>
+    <definedName name="tecnico">CRITÉRIOS!$A$14:$A$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="44" r:id="rId7"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -45,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="152">
   <si>
     <t>FUNCIONÁRIO</t>
   </si>
@@ -440,29 +468,79 @@
     <t>#=DATADIF(E3;HOJE();"Y") - usando a função data dif</t>
   </si>
   <si>
-    <t>ctrl + / para adicionar uma linha</t>
-  </si>
-  <si>
     <t>#=INT((HOJE()-E3)/365,25) (EM ANOS)</t>
   </si>
   <si>
-    <t>funções</t>
-  </si>
-  <si>
     <t>#=BDSOMA(DADOS;salario;ADM)</t>
+  </si>
+  <si>
+    <t>"ctrl +"  =  para adicionar uma linha</t>
+  </si>
+  <si>
+    <t>#=BDMÉDIA(DADOS;salario;ADM)</t>
+  </si>
+  <si>
+    <t>#=BDMÁX(DADOS;salario;ADM)</t>
+  </si>
+  <si>
+    <t>#=BDMÍN(DADOS;salario;ADM)</t>
+  </si>
+  <si>
+    <t>#=BDCONTAR(DADOS;salario;ADM)</t>
+  </si>
+  <si>
+    <t>Salário</t>
+  </si>
+  <si>
+    <t>←Máx</t>
+  </si>
+  <si>
+    <t>←Min</t>
+  </si>
+  <si>
+    <t>#=BDEXTRAIR(DADOS;funcionario;adm_max_sal)</t>
+  </si>
+  <si>
+    <t>#=BDEXTRAIR(DADOS;funcionario;adm_min_sal)</t>
+  </si>
+  <si>
+    <t>Idade</t>
+  </si>
+  <si>
+    <t>Rótulos de Linha</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>Soma de SALÁRIO</t>
+  </si>
+  <si>
+    <t>Soma de IDADE</t>
+  </si>
+  <si>
+    <t>(Tudo)</t>
+  </si>
+  <si>
+    <t>Média de SALÁRIO2</t>
+  </si>
+  <si>
+    <t>Máx. de SALÁRIO2</t>
+  </si>
+  <si>
+    <t>Mín. de SALÁRIO2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -529,8 +607,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -576,6 +662,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -648,7 +764,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -671,10 +787,45 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="11" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -687,29 +838,20 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Moeda" xfId="2" builtinId="4"/>
@@ -734,6 +876,2560 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="YURI DA SILVA MENDES" refreshedDate="46300.902255092595" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="102" xr:uid="{4360A9BA-6F54-4C96-9D03-92FEC243F4C1}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A2:F104" sheet="CADASTRO"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="FUNCIONÁRIO" numFmtId="0">
+      <sharedItems count="102">
+        <s v="Alan Golden"/>
+        <s v="Amanda Colares"/>
+        <s v="Aline Moreno"/>
+        <s v="Fernando Pas"/>
+        <s v="Ana Cristina Paiva"/>
+        <s v="Ana Maria Bernardes"/>
+        <s v="Angélica Bueno"/>
+        <s v="Arlete Farias"/>
+        <s v="Barbara Hioli"/>
+        <s v="Beatriz Domingues"/>
+        <s v="Beatriz Saracena"/>
+        <s v="Bernardo Lima"/>
+        <s v="Camila Gonçalves"/>
+        <s v="Catarina Big"/>
+        <s v="Cecilia Nartolli"/>
+        <s v="Diógenes Duarte Lima"/>
+        <s v="Jussara Medeiros"/>
+        <s v="Felipe dos Santos"/>
+        <s v="Fernanda Marioni"/>
+        <s v="Fernando Alencar"/>
+        <s v="Fernando Augusto Martinez"/>
+        <s v="Fernando Coriolano"/>
+        <s v="Fabiana Soares"/>
+        <s v="Gabriel Kresko"/>
+        <s v="Galdencio Hurita"/>
+        <s v="Georgina Nythe"/>
+        <s v="Geraldo Maximiliano"/>
+        <s v="Gilda Soares"/>
+        <s v="Hector Beliz"/>
+        <s v="Hector Mangiolii"/>
+        <s v="Henrique Girardi"/>
+        <s v="Heraldo Ferreira"/>
+        <s v="Homero Gamberin"/>
+        <s v="Inês Souza"/>
+        <s v="Vera Barroso"/>
+        <s v="Isabella Raquieri"/>
+        <s v="Jaciara Yonh"/>
+        <s v="Jade Vinilitti"/>
+        <s v="João Alves"/>
+        <s v="João Moreira"/>
+        <s v="João Paulo Almeida"/>
+        <s v="Joaquim Nabuco"/>
+        <s v="Alexandre Garcia Gomes"/>
+        <s v="Jurandir Ricce"/>
+        <s v="Sonia Ferreira"/>
+        <s v="Karen Rodrigues"/>
+        <s v="Karina Medeiros"/>
+        <s v="Katia Domenica Lira"/>
+        <s v="Katrina Feijó"/>
+        <s v="Lorival Hernandes"/>
+        <s v="Luci Pereira"/>
+        <s v="Luciana Meirelles"/>
+        <s v="Luis Gabriel Norub"/>
+        <s v="Luiz André Ferreira"/>
+        <s v="Isabel Garcia"/>
+        <s v="Maraluce Gomes"/>
+        <s v="Marcela Gianotti"/>
+        <s v="Marcelo Aguiar"/>
+        <s v="Márcia Giuliani"/>
+        <s v="Marco Aurélio da Silva"/>
+        <s v="Marcos Albuquerque"/>
+        <s v="Marcos Assunção"/>
+        <s v="Maria Amélia Gouveia"/>
+        <s v="Maria Carolina Braga"/>
+        <s v="Maria Cilene Souza"/>
+        <s v="Maria do Carmo Leal"/>
+        <s v="Maria Inês Fagundes"/>
+        <s v="Maria Lucia Medeiros"/>
+        <s v="Maria Luiza Nasser"/>
+        <s v="Marina Santana"/>
+        <s v="Marineide Novais"/>
+        <s v="Marli Farias"/>
+        <s v="Marli Vieira "/>
+        <s v="Máximo Queiroz"/>
+        <s v="Melina Mercurio"/>
+        <s v="Miriam Hashimoto"/>
+        <s v="Nelson Cavaleiro"/>
+        <s v="Noeli Fernandes"/>
+        <s v="Ricardo Araras"/>
+        <s v="Rodrigo Maia"/>
+        <s v="Rogerio Dias"/>
+        <s v="Rogério Hanibal Junior"/>
+        <s v="Ronaldo Antunes"/>
+        <s v="Rosa Maria Garibaldo"/>
+        <s v="Rosana Gabrielli"/>
+        <s v="Roseli Hernandes"/>
+        <s v="Roseli Marcondes"/>
+        <s v="Roseli Mariachi"/>
+        <s v="Sofia Barros Maranhão"/>
+        <s v="Solange Farias"/>
+        <s v="Jocelyn Camargo"/>
+        <s v="Sonia Maria Pereira"/>
+        <s v="Stella Cruz e Souza"/>
+        <s v="Stella Maris"/>
+        <s v="Tabata Genovich"/>
+        <s v="Tomás Ferraz"/>
+        <s v="Ursula Hiroshi"/>
+        <s v="Vanda Sueres"/>
+        <s v="Vanderlei Higino"/>
+        <s v="Vanessa Silva e Souza"/>
+        <s v="Manoel Guimarães"/>
+        <s v="Yeda Farias"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="DEPARTAMENTO" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Recursos Humanos"/>
+        <s v="Administrativo"/>
+        <s v="Financeiro"/>
+        <s v="Informática"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="CARGO" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Assistente"/>
+        <s v="Técnico"/>
+        <s v="Gerente"/>
+        <s v="Analista"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="SALÁRIO" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="890" maxValue="4780"/>
+    </cacheField>
+    <cacheField name="DATA NASCIMENTO" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="1956-09-16T00:00:00" maxDate="1992-01-03T00:00:00" count="102">
+        <d v="1992-01-02T00:00:00"/>
+        <d v="1991-09-20T00:00:00"/>
+        <d v="1978-05-13T00:00:00"/>
+        <d v="1990-11-22T00:00:00"/>
+        <d v="1965-10-12T00:00:00"/>
+        <d v="1989-11-15T00:00:00"/>
+        <d v="1977-06-26T00:00:00"/>
+        <d v="1966-04-12T00:00:00"/>
+        <d v="1967-02-28T00:00:00"/>
+        <d v="1984-03-18T00:00:00"/>
+        <d v="1990-06-29T00:00:00"/>
+        <d v="1985-07-30T00:00:00"/>
+        <d v="1984-08-11T00:00:00"/>
+        <d v="1979-01-12T00:00:00"/>
+        <d v="1980-02-14T00:00:00"/>
+        <d v="1959-05-11T00:00:00"/>
+        <d v="1991-09-24T00:00:00"/>
+        <d v="1988-12-16T00:00:00"/>
+        <d v="1960-01-21T00:00:00"/>
+        <d v="1990-03-15T00:00:00"/>
+        <d v="1985-01-25T00:00:00"/>
+        <d v="1968-04-30T00:00:00"/>
+        <d v="1987-08-17T00:00:00"/>
+        <d v="1978-10-14T00:00:00"/>
+        <d v="1976-09-26T00:00:00"/>
+        <d v="1989-05-12T00:00:00"/>
+        <d v="1979-06-16T00:00:00"/>
+        <d v="1960-11-15T00:00:00"/>
+        <d v="1983-03-31T00:00:00"/>
+        <d v="1982-07-04T00:00:00"/>
+        <d v="1985-12-31T00:00:00"/>
+        <d v="1980-11-05T00:00:00"/>
+        <d v="1984-04-04T00:00:00"/>
+        <d v="1978-09-23T00:00:00"/>
+        <d v="1986-12-07T00:00:00"/>
+        <d v="1967-06-12T00:00:00"/>
+        <d v="1956-09-16T00:00:00"/>
+        <d v="1981-06-01T00:00:00"/>
+        <d v="1967-10-17T00:00:00"/>
+        <d v="1980-10-10T00:00:00"/>
+        <d v="1990-05-25T00:00:00"/>
+        <d v="1982-11-24T00:00:00"/>
+        <d v="1987-06-12T00:00:00"/>
+        <d v="1977-03-23T00:00:00"/>
+        <d v="1987-05-03T00:00:00"/>
+        <d v="1974-05-17T00:00:00"/>
+        <d v="1990-03-16T00:00:00"/>
+        <d v="1982-12-04T00:00:00"/>
+        <d v="1988-10-26T00:00:00"/>
+        <d v="1969-04-15T00:00:00"/>
+        <d v="1988-09-05T00:00:00"/>
+        <d v="1977-03-31T00:00:00"/>
+        <d v="1978-08-06T00:00:00"/>
+        <d v="1981-07-04T00:00:00"/>
+        <d v="1986-10-22T00:00:00"/>
+        <d v="1983-12-12T00:00:00"/>
+        <d v="1981-07-15T00:00:00"/>
+        <d v="1977-02-05T00:00:00"/>
+        <d v="1984-11-08T00:00:00"/>
+        <d v="1988-05-10T00:00:00"/>
+        <d v="1968-02-14T00:00:00"/>
+        <d v="1984-09-28T00:00:00"/>
+        <d v="1973-12-19T00:00:00"/>
+        <d v="1980-09-22T00:00:00"/>
+        <d v="1969-07-18T00:00:00"/>
+        <d v="1983-05-22T00:00:00"/>
+        <d v="1980-01-01T00:00:00"/>
+        <d v="1982-10-16T00:00:00"/>
+        <d v="1988-08-08T00:00:00"/>
+        <d v="1984-09-18T00:00:00"/>
+        <d v="1974-04-25T00:00:00"/>
+        <d v="1968-09-05T00:00:00"/>
+        <d v="1989-11-20T00:00:00"/>
+        <d v="1979-06-27T00:00:00"/>
+        <d v="1983-09-25T00:00:00"/>
+        <d v="1970-10-16T00:00:00"/>
+        <d v="1989-01-06T00:00:00"/>
+        <d v="1980-11-15T00:00:00"/>
+        <d v="1979-12-05T00:00:00"/>
+        <d v="1983-03-03T00:00:00"/>
+        <d v="1978-12-02T00:00:00"/>
+        <d v="1989-07-14T00:00:00"/>
+        <d v="1980-05-28T00:00:00"/>
+        <d v="1989-10-02T00:00:00"/>
+        <d v="1985-01-20T00:00:00"/>
+        <d v="1985-03-03T00:00:00"/>
+        <d v="1978-10-04T00:00:00"/>
+        <d v="1989-10-22T00:00:00"/>
+        <d v="1985-05-25T00:00:00"/>
+        <d v="1981-07-22T00:00:00"/>
+        <d v="1986-12-10T00:00:00"/>
+        <d v="1982-11-12T00:00:00"/>
+        <d v="1985-06-14T00:00:00"/>
+        <d v="1989-08-01T00:00:00"/>
+        <d v="1984-05-04T00:00:00"/>
+        <d v="1968-10-06T00:00:00"/>
+        <d v="1989-08-29T00:00:00"/>
+        <d v="1975-04-03T00:00:00"/>
+        <d v="1983-03-30T00:00:00"/>
+        <d v="1979-02-28T00:00:00"/>
+        <d v="1987-10-02T00:00:00"/>
+        <d v="1989-11-23T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="8"/>
+    </cacheField>
+    <cacheField name="IDADE" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="34" maxValue="70" count="28">
+        <n v="34"/>
+        <n v="35"/>
+        <n v="48"/>
+        <n v="60"/>
+        <n v="36"/>
+        <n v="49"/>
+        <n v="59"/>
+        <n v="42"/>
+        <n v="41"/>
+        <n v="47"/>
+        <n v="46"/>
+        <n v="67"/>
+        <n v="37"/>
+        <n v="66"/>
+        <n v="58"/>
+        <n v="39"/>
+        <n v="50"/>
+        <n v="65"/>
+        <n v="43"/>
+        <n v="44"/>
+        <n v="40"/>
+        <n v="45"/>
+        <n v="70"/>
+        <n v="52"/>
+        <n v="57"/>
+        <n v="38"/>
+        <n v="55"/>
+        <n v="51"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Meses (DATA NASCIMENTO)" numFmtId="0" databaseField="0">
+      <fieldGroup base="4">
+        <rangePr groupBy="months" startDate="1956-09-16T00:00:00" endDate="1992-01-03T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;16/09/1956"/>
+          <s v="jan"/>
+          <s v="fev"/>
+          <s v="mar"/>
+          <s v="abr"/>
+          <s v="mai"/>
+          <s v="jun"/>
+          <s v="jul"/>
+          <s v="ago"/>
+          <s v="set"/>
+          <s v="out"/>
+          <s v="nov"/>
+          <s v="dez"/>
+          <s v="&gt;03/01/1992"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Trimestres (DATA NASCIMENTO)" numFmtId="0" databaseField="0">
+      <fieldGroup base="4">
+        <rangePr groupBy="quarters" startDate="1956-09-16T00:00:00" endDate="1992-01-03T00:00:00"/>
+        <groupItems count="6">
+          <s v="&lt;16/09/1956"/>
+          <s v="Trim1"/>
+          <s v="Trim2"/>
+          <s v="Trim3"/>
+          <s v="Trim4"/>
+          <s v="&gt;03/01/1992"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Anos (DATA NASCIMENTO)" numFmtId="0" databaseField="0">
+      <fieldGroup base="4">
+        <rangePr groupBy="years" startDate="1956-09-16T00:00:00" endDate="1992-01-03T00:00:00"/>
+        <groupItems count="39">
+          <s v="&lt;16/09/1956"/>
+          <s v="1956"/>
+          <s v="1957"/>
+          <s v="1958"/>
+          <s v="1959"/>
+          <s v="1960"/>
+          <s v="1961"/>
+          <s v="1962"/>
+          <s v="1963"/>
+          <s v="1964"/>
+          <s v="1965"/>
+          <s v="1966"/>
+          <s v="1967"/>
+          <s v="1968"/>
+          <s v="1969"/>
+          <s v="1970"/>
+          <s v="1971"/>
+          <s v="1972"/>
+          <s v="1973"/>
+          <s v="1974"/>
+          <s v="1975"/>
+          <s v="1976"/>
+          <s v="1977"/>
+          <s v="1978"/>
+          <s v="1979"/>
+          <s v="1980"/>
+          <s v="1981"/>
+          <s v="1982"/>
+          <s v="1983"/>
+          <s v="1984"/>
+          <s v="1985"/>
+          <s v="1986"/>
+          <s v="1987"/>
+          <s v="1988"/>
+          <s v="1989"/>
+          <s v="1990"/>
+          <s v="1991"/>
+          <s v="1992"/>
+          <s v="&gt;03/01/1992"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="102">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2300"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1250"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2100"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1560"/>
+    <x v="3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="4000"/>
+    <x v="4"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2700"/>
+    <x v="5"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1800"/>
+    <x v="6"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1750"/>
+    <x v="7"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2470"/>
+    <x v="8"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="1678"/>
+    <x v="9"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2790"/>
+    <x v="10"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="2000"/>
+    <x v="11"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="3500"/>
+    <x v="12"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2700"/>
+    <x v="13"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2780"/>
+    <x v="14"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="4500"/>
+    <x v="15"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2640"/>
+    <x v="16"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1207"/>
+    <x v="17"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="4780"/>
+    <x v="18"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="3200"/>
+    <x v="19"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1450"/>
+    <x v="20"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2769"/>
+    <x v="21"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1200"/>
+    <x v="22"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1564"/>
+    <x v="23"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1800"/>
+    <x v="24"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="4200"/>
+    <x v="25"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1458"/>
+    <x v="26"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="3200"/>
+    <x v="27"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="3600"/>
+    <x v="28"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="3190"/>
+    <x v="29"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1400"/>
+    <x v="30"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2180"/>
+    <x v="31"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="2570"/>
+    <x v="32"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="1320"/>
+    <x v="33"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2390"/>
+    <x v="34"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="3200"/>
+    <x v="35"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="2100"/>
+    <x v="36"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1890"/>
+    <x v="37"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2650"/>
+    <x v="38"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="2850"/>
+    <x v="39"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2176"/>
+    <x v="40"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1050"/>
+    <x v="41"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2500"/>
+    <x v="42"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="2100"/>
+    <x v="43"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2900"/>
+    <x v="44"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1000"/>
+    <x v="45"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2980"/>
+    <x v="46"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="2000"/>
+    <x v="47"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2100"/>
+    <x v="48"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1250"/>
+    <x v="49"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="3000"/>
+    <x v="50"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="3010"/>
+    <x v="51"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1100"/>
+    <x v="52"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2040"/>
+    <x v="53"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1600"/>
+    <x v="54"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2100"/>
+    <x v="55"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2900"/>
+    <x v="56"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2000"/>
+    <x v="57"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1980"/>
+    <x v="58"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="3100"/>
+    <x v="59"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="60"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2980"/>
+    <x v="60"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="61"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="2890"/>
+    <x v="61"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="62"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1100"/>
+    <x v="62"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="63"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2950"/>
+    <x v="63"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="64"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2400"/>
+    <x v="64"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="65"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="980"/>
+    <x v="65"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="66"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="950"/>
+    <x v="66"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="67"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1945"/>
+    <x v="67"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="68"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="3000"/>
+    <x v="68"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="69"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="3050"/>
+    <x v="69"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="70"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="956"/>
+    <x v="70"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="71"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="990"/>
+    <x v="71"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="72"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2560"/>
+    <x v="72"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="73"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2760"/>
+    <x v="73"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="74"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2780"/>
+    <x v="74"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="75"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2850"/>
+    <x v="75"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="76"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1060"/>
+    <x v="76"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="77"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1000"/>
+    <x v="77"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="78"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2450"/>
+    <x v="78"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="79"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="2900"/>
+    <x v="79"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="80"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="890"/>
+    <x v="80"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="81"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2100"/>
+    <x v="81"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="82"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2764"/>
+    <x v="82"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="83"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1560"/>
+    <x v="83"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="84"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1035"/>
+    <x v="84"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="85"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1790"/>
+    <x v="85"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="86"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="1945"/>
+    <x v="86"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="87"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2740"/>
+    <x v="87"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="88"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="3100"/>
+    <x v="88"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="89"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2109"/>
+    <x v="89"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="90"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1320"/>
+    <x v="90"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="91"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2100"/>
+    <x v="91"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="92"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1090"/>
+    <x v="92"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="93"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="3120"/>
+    <x v="93"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="94"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2100"/>
+    <x v="94"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="95"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="3000"/>
+    <x v="95"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="96"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="896"/>
+    <x v="96"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="97"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="1000"/>
+    <x v="97"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="98"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1107"/>
+    <x v="98"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="99"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1980"/>
+    <x v="99"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="100"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1020"/>
+    <x v="100"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="101"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2480"/>
+    <x v="101"/>
+    <x v="4"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1654B947-5549-4CA7-8178-CD4D120B1567}" name="Tabela dinâmica1" cacheId="44" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:F110" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="103">
+        <item x="0"/>
+        <item x="42"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="22"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="54"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="90"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="100"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="44"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="34"/>
+        <item x="101"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="103">
+        <item x="36"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="27"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="35"/>
+        <item x="38"/>
+        <item x="60"/>
+        <item x="21"/>
+        <item x="71"/>
+        <item x="95"/>
+        <item x="49"/>
+        <item x="64"/>
+        <item x="75"/>
+        <item x="62"/>
+        <item x="70"/>
+        <item x="45"/>
+        <item x="97"/>
+        <item x="24"/>
+        <item x="57"/>
+        <item x="43"/>
+        <item x="51"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="52"/>
+        <item x="33"/>
+        <item x="86"/>
+        <item x="23"/>
+        <item x="80"/>
+        <item x="13"/>
+        <item x="99"/>
+        <item x="26"/>
+        <item x="73"/>
+        <item x="78"/>
+        <item x="66"/>
+        <item x="14"/>
+        <item x="82"/>
+        <item x="63"/>
+        <item x="39"/>
+        <item x="31"/>
+        <item x="77"/>
+        <item x="37"/>
+        <item x="53"/>
+        <item x="56"/>
+        <item x="89"/>
+        <item x="29"/>
+        <item x="67"/>
+        <item x="91"/>
+        <item x="41"/>
+        <item x="47"/>
+        <item x="79"/>
+        <item x="98"/>
+        <item x="28"/>
+        <item x="65"/>
+        <item x="74"/>
+        <item x="55"/>
+        <item x="9"/>
+        <item x="32"/>
+        <item x="94"/>
+        <item x="12"/>
+        <item x="69"/>
+        <item x="61"/>
+        <item x="58"/>
+        <item x="84"/>
+        <item x="20"/>
+        <item x="85"/>
+        <item x="88"/>
+        <item x="92"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="54"/>
+        <item x="34"/>
+        <item x="90"/>
+        <item x="44"/>
+        <item x="42"/>
+        <item x="22"/>
+        <item x="100"/>
+        <item x="59"/>
+        <item x="68"/>
+        <item x="50"/>
+        <item x="48"/>
+        <item x="17"/>
+        <item x="76"/>
+        <item x="25"/>
+        <item x="81"/>
+        <item x="93"/>
+        <item x="96"/>
+        <item x="83"/>
+        <item x="87"/>
+        <item x="5"/>
+        <item x="72"/>
+        <item x="101"/>
+        <item x="19"/>
+        <item x="46"/>
+        <item x="40"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="40">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="107">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="38"/>
+    </i>
+    <i r="1">
+      <x v="40"/>
+    </i>
+    <i r="1">
+      <x v="43"/>
+    </i>
+    <i r="1">
+      <x v="48"/>
+    </i>
+    <i r="1">
+      <x v="49"/>
+    </i>
+    <i r="1">
+      <x v="52"/>
+    </i>
+    <i r="1">
+      <x v="53"/>
+    </i>
+    <i r="1">
+      <x v="55"/>
+    </i>
+    <i r="1">
+      <x v="58"/>
+    </i>
+    <i r="1">
+      <x v="62"/>
+    </i>
+    <i r="1">
+      <x v="64"/>
+    </i>
+    <i r="1">
+      <x v="67"/>
+    </i>
+    <i r="1">
+      <x v="73"/>
+    </i>
+    <i r="1">
+      <x v="74"/>
+    </i>
+    <i r="1">
+      <x v="78"/>
+    </i>
+    <i r="1">
+      <x v="79"/>
+    </i>
+    <i r="1">
+      <x v="80"/>
+    </i>
+    <i r="1">
+      <x v="83"/>
+    </i>
+    <i r="1">
+      <x v="85"/>
+    </i>
+    <i r="1">
+      <x v="86"/>
+    </i>
+    <i r="1">
+      <x v="91"/>
+    </i>
+    <i r="1">
+      <x v="96"/>
+    </i>
+    <i r="1">
+      <x v="100"/>
+    </i>
+    <i r="1">
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+    </i>
+    <i r="1">
+      <x v="51"/>
+    </i>
+    <i r="1">
+      <x v="57"/>
+    </i>
+    <i r="1">
+      <x v="60"/>
+    </i>
+    <i r="1">
+      <x v="65"/>
+    </i>
+    <i r="1">
+      <x v="68"/>
+    </i>
+    <i r="1">
+      <x v="72"/>
+    </i>
+    <i r="1">
+      <x v="75"/>
+    </i>
+    <i r="1">
+      <x v="81"/>
+    </i>
+    <i r="1">
+      <x v="89"/>
+    </i>
+    <i r="1">
+      <x v="90"/>
+    </i>
+    <i r="1">
+      <x v="94"/>
+    </i>
+    <i r="1">
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i r="1">
+      <x v="34"/>
+    </i>
+    <i r="1">
+      <x v="35"/>
+    </i>
+    <i r="1">
+      <x v="39"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+    </i>
+    <i r="1">
+      <x v="42"/>
+    </i>
+    <i r="1">
+      <x v="54"/>
+    </i>
+    <i r="1">
+      <x v="61"/>
+    </i>
+    <i r="1">
+      <x v="66"/>
+    </i>
+    <i r="1">
+      <x v="71"/>
+    </i>
+    <i r="1">
+      <x v="77"/>
+    </i>
+    <i r="1">
+      <x v="84"/>
+    </i>
+    <i r="1">
+      <x v="88"/>
+    </i>
+    <i r="1">
+      <x v="95"/>
+    </i>
+    <i r="1">
+      <x v="99"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="37"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+    </i>
+    <i r="1">
+      <x v="46"/>
+    </i>
+    <i r="1">
+      <x v="50"/>
+    </i>
+    <i r="1">
+      <x v="56"/>
+    </i>
+    <i r="1">
+      <x v="59"/>
+    </i>
+    <i r="1">
+      <x v="63"/>
+    </i>
+    <i r="1">
+      <x v="69"/>
+    </i>
+    <i r="1">
+      <x v="70"/>
+    </i>
+    <i r="1">
+      <x v="76"/>
+    </i>
+    <i r="1">
+      <x v="82"/>
+    </i>
+    <i r="1">
+      <x v="87"/>
+    </i>
+    <i r="1">
+      <x v="92"/>
+    </i>
+    <i r="1">
+      <x v="93"/>
+    </i>
+    <i r="1">
+      <x v="98"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+  </colItems>
+  <dataFields count="5">
+    <dataField name="Soma de SALÁRIO" fld="3" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="Média de SALÁRIO2" fld="3" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="Máx. de SALÁRIO2" fld="3" subtotal="max" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="Mín. de SALÁRIO2" fld="3" subtotal="min" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="Soma de IDADE" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{36E7EE18-E20B-47AE-B1FA-7F0FAE4FC2C5}" name="Tabela dinâmica2" cacheId="44" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:C111" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="103">
+        <item x="0"/>
+        <item x="42"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="22"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="54"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="90"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="100"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="44"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="34"/>
+        <item x="101"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="103">
+        <item x="36"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="27"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="35"/>
+        <item x="38"/>
+        <item x="60"/>
+        <item x="21"/>
+        <item x="71"/>
+        <item x="95"/>
+        <item x="49"/>
+        <item x="64"/>
+        <item x="75"/>
+        <item x="62"/>
+        <item x="70"/>
+        <item x="45"/>
+        <item x="97"/>
+        <item x="24"/>
+        <item x="57"/>
+        <item x="43"/>
+        <item x="51"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="52"/>
+        <item x="33"/>
+        <item x="86"/>
+        <item x="23"/>
+        <item x="80"/>
+        <item x="13"/>
+        <item x="99"/>
+        <item x="26"/>
+        <item x="73"/>
+        <item x="78"/>
+        <item x="66"/>
+        <item x="14"/>
+        <item x="82"/>
+        <item x="63"/>
+        <item x="39"/>
+        <item x="31"/>
+        <item x="77"/>
+        <item x="37"/>
+        <item x="53"/>
+        <item x="56"/>
+        <item x="89"/>
+        <item x="29"/>
+        <item x="67"/>
+        <item x="91"/>
+        <item x="41"/>
+        <item x="47"/>
+        <item x="79"/>
+        <item x="98"/>
+        <item x="28"/>
+        <item x="65"/>
+        <item x="74"/>
+        <item x="55"/>
+        <item x="9"/>
+        <item x="32"/>
+        <item x="94"/>
+        <item x="12"/>
+        <item x="69"/>
+        <item x="61"/>
+        <item x="58"/>
+        <item x="84"/>
+        <item x="20"/>
+        <item x="85"/>
+        <item x="88"/>
+        <item x="92"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="54"/>
+        <item x="34"/>
+        <item x="90"/>
+        <item x="44"/>
+        <item x="42"/>
+        <item x="22"/>
+        <item x="100"/>
+        <item x="59"/>
+        <item x="68"/>
+        <item x="50"/>
+        <item x="48"/>
+        <item x="17"/>
+        <item x="76"/>
+        <item x="25"/>
+        <item x="81"/>
+        <item x="93"/>
+        <item x="96"/>
+        <item x="83"/>
+        <item x="87"/>
+        <item x="5"/>
+        <item x="72"/>
+        <item x="101"/>
+        <item x="19"/>
+        <item x="46"/>
+        <item x="40"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="25"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="26"/>
+        <item x="24"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="22"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="6">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="39">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="107">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="38"/>
+    </i>
+    <i r="1">
+      <x v="40"/>
+    </i>
+    <i r="1">
+      <x v="43"/>
+    </i>
+    <i r="1">
+      <x v="48"/>
+    </i>
+    <i r="1">
+      <x v="49"/>
+    </i>
+    <i r="1">
+      <x v="52"/>
+    </i>
+    <i r="1">
+      <x v="53"/>
+    </i>
+    <i r="1">
+      <x v="55"/>
+    </i>
+    <i r="1">
+      <x v="58"/>
+    </i>
+    <i r="1">
+      <x v="62"/>
+    </i>
+    <i r="1">
+      <x v="64"/>
+    </i>
+    <i r="1">
+      <x v="67"/>
+    </i>
+    <i r="1">
+      <x v="73"/>
+    </i>
+    <i r="1">
+      <x v="74"/>
+    </i>
+    <i r="1">
+      <x v="78"/>
+    </i>
+    <i r="1">
+      <x v="79"/>
+    </i>
+    <i r="1">
+      <x v="80"/>
+    </i>
+    <i r="1">
+      <x v="83"/>
+    </i>
+    <i r="1">
+      <x v="85"/>
+    </i>
+    <i r="1">
+      <x v="86"/>
+    </i>
+    <i r="1">
+      <x v="91"/>
+    </i>
+    <i r="1">
+      <x v="96"/>
+    </i>
+    <i r="1">
+      <x v="100"/>
+    </i>
+    <i r="1">
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+    </i>
+    <i r="1">
+      <x v="51"/>
+    </i>
+    <i r="1">
+      <x v="57"/>
+    </i>
+    <i r="1">
+      <x v="60"/>
+    </i>
+    <i r="1">
+      <x v="65"/>
+    </i>
+    <i r="1">
+      <x v="68"/>
+    </i>
+    <i r="1">
+      <x v="72"/>
+    </i>
+    <i r="1">
+      <x v="75"/>
+    </i>
+    <i r="1">
+      <x v="81"/>
+    </i>
+    <i r="1">
+      <x v="89"/>
+    </i>
+    <i r="1">
+      <x v="90"/>
+    </i>
+    <i r="1">
+      <x v="94"/>
+    </i>
+    <i r="1">
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i r="1">
+      <x v="34"/>
+    </i>
+    <i r="1">
+      <x v="35"/>
+    </i>
+    <i r="1">
+      <x v="39"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+    </i>
+    <i r="1">
+      <x v="42"/>
+    </i>
+    <i r="1">
+      <x v="54"/>
+    </i>
+    <i r="1">
+      <x v="61"/>
+    </i>
+    <i r="1">
+      <x v="66"/>
+    </i>
+    <i r="1">
+      <x v="71"/>
+    </i>
+    <i r="1">
+      <x v="77"/>
+    </i>
+    <i r="1">
+      <x v="84"/>
+    </i>
+    <i r="1">
+      <x v="88"/>
+    </i>
+    <i r="1">
+      <x v="95"/>
+    </i>
+    <i r="1">
+      <x v="99"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="37"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+    </i>
+    <i r="1">
+      <x v="46"/>
+    </i>
+    <i r="1">
+      <x v="50"/>
+    </i>
+    <i r="1">
+      <x v="56"/>
+    </i>
+    <i r="1">
+      <x v="59"/>
+    </i>
+    <i r="1">
+      <x v="63"/>
+    </i>
+    <i r="1">
+      <x v="69"/>
+    </i>
+    <i r="1">
+      <x v="70"/>
+    </i>
+    <i r="1">
+      <x v="76"/>
+    </i>
+    <i r="1">
+      <x v="82"/>
+    </i>
+    <i r="1">
+      <x v="87"/>
+    </i>
+    <i r="1">
+      <x v="92"/>
+    </i>
+    <i r="1">
+      <x v="93"/>
+    </i>
+    <i r="1">
+      <x v="98"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Soma de SALÁRIO" fld="3" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="Soma de IDADE" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleDark13" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1022,30 +3718,3510 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F435B4C4-BA9D-4E26-ABC8-72265E64F55E}">
+  <dimension ref="A3:F110"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="29" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="57" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="85" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="17" bestFit="1" customWidth="1"/>
+    <col min="87" max="113" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="22.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="46">
+        <v>66891</v>
+      </c>
+      <c r="C4" s="46">
+        <v>1967.3823529411766</v>
+      </c>
+      <c r="D4" s="46">
+        <v>4000</v>
+      </c>
+      <c r="E4" s="46">
+        <v>890</v>
+      </c>
+      <c r="F4" s="41">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="46">
+        <v>1250</v>
+      </c>
+      <c r="C5" s="46">
+        <v>1250</v>
+      </c>
+      <c r="D5" s="46">
+        <v>1250</v>
+      </c>
+      <c r="E5" s="46">
+        <v>1250</v>
+      </c>
+      <c r="F5" s="41">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="46">
+        <v>4000</v>
+      </c>
+      <c r="C6" s="46">
+        <v>4000</v>
+      </c>
+      <c r="D6" s="46">
+        <v>4000</v>
+      </c>
+      <c r="E6" s="46">
+        <v>4000</v>
+      </c>
+      <c r="F6" s="41">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="46">
+        <v>1678</v>
+      </c>
+      <c r="C7" s="46">
+        <v>1678</v>
+      </c>
+      <c r="D7" s="46">
+        <v>1678</v>
+      </c>
+      <c r="E7" s="46">
+        <v>1678</v>
+      </c>
+      <c r="F7" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="46">
+        <v>1200</v>
+      </c>
+      <c r="C8" s="46">
+        <v>1200</v>
+      </c>
+      <c r="D8" s="46">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="46">
+        <v>1200</v>
+      </c>
+      <c r="F8" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="46">
+        <v>1207</v>
+      </c>
+      <c r="C9" s="46">
+        <v>1207</v>
+      </c>
+      <c r="D9" s="46">
+        <v>1207</v>
+      </c>
+      <c r="E9" s="46">
+        <v>1207</v>
+      </c>
+      <c r="F9" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="46">
+        <v>1560</v>
+      </c>
+      <c r="C10" s="46">
+        <v>1560</v>
+      </c>
+      <c r="D10" s="46">
+        <v>1560</v>
+      </c>
+      <c r="E10" s="46">
+        <v>1560</v>
+      </c>
+      <c r="F10" s="41">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="46">
+        <v>1564</v>
+      </c>
+      <c r="C11" s="46">
+        <v>1564</v>
+      </c>
+      <c r="D11" s="46">
+        <v>1564</v>
+      </c>
+      <c r="E11" s="46">
+        <v>1564</v>
+      </c>
+      <c r="F11" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="46">
+        <v>1800</v>
+      </c>
+      <c r="C12" s="46">
+        <v>1800</v>
+      </c>
+      <c r="D12" s="46">
+        <v>1800</v>
+      </c>
+      <c r="E12" s="46">
+        <v>1800</v>
+      </c>
+      <c r="F12" s="41">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="46">
+        <v>2180</v>
+      </c>
+      <c r="C13" s="46">
+        <v>2180</v>
+      </c>
+      <c r="D13" s="46">
+        <v>2180</v>
+      </c>
+      <c r="E13" s="46">
+        <v>2180</v>
+      </c>
+      <c r="F13" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="46">
+        <v>2570</v>
+      </c>
+      <c r="C14" s="46">
+        <v>2570</v>
+      </c>
+      <c r="D14" s="46">
+        <v>2570</v>
+      </c>
+      <c r="E14" s="46">
+        <v>2570</v>
+      </c>
+      <c r="F14" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="46">
+        <v>2650</v>
+      </c>
+      <c r="C15" s="46">
+        <v>2650</v>
+      </c>
+      <c r="D15" s="46">
+        <v>2650</v>
+      </c>
+      <c r="E15" s="46">
+        <v>2650</v>
+      </c>
+      <c r="F15" s="41">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="46">
+        <v>2176</v>
+      </c>
+      <c r="C16" s="46">
+        <v>2176</v>
+      </c>
+      <c r="D16" s="46">
+        <v>2176</v>
+      </c>
+      <c r="E16" s="46">
+        <v>2176</v>
+      </c>
+      <c r="F16" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C17" s="46">
+        <v>2100</v>
+      </c>
+      <c r="D17" s="46">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="46">
+        <v>2100</v>
+      </c>
+      <c r="F17" s="41">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C18" s="46">
+        <v>2100</v>
+      </c>
+      <c r="D18" s="46">
+        <v>2100</v>
+      </c>
+      <c r="E18" s="46">
+        <v>2100</v>
+      </c>
+      <c r="F18" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="46">
+        <v>1250</v>
+      </c>
+      <c r="C19" s="46">
+        <v>1250</v>
+      </c>
+      <c r="D19" s="46">
+        <v>1250</v>
+      </c>
+      <c r="E19" s="46">
+        <v>1250</v>
+      </c>
+      <c r="F19" s="41">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="46">
+        <v>1100</v>
+      </c>
+      <c r="C20" s="46">
+        <v>1100</v>
+      </c>
+      <c r="D20" s="46">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="46">
+        <v>1100</v>
+      </c>
+      <c r="F20" s="41">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="46">
+        <v>2040</v>
+      </c>
+      <c r="C21" s="46">
+        <v>2040</v>
+      </c>
+      <c r="D21" s="46">
+        <v>2040</v>
+      </c>
+      <c r="E21" s="46">
+        <v>2040</v>
+      </c>
+      <c r="F21" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C22" s="46">
+        <v>2100</v>
+      </c>
+      <c r="D22" s="46">
+        <v>2100</v>
+      </c>
+      <c r="E22" s="46">
+        <v>2100</v>
+      </c>
+      <c r="F22" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="46">
+        <v>1980</v>
+      </c>
+      <c r="C23" s="46">
+        <v>1980</v>
+      </c>
+      <c r="D23" s="46">
+        <v>1980</v>
+      </c>
+      <c r="E23" s="46">
+        <v>1980</v>
+      </c>
+      <c r="F23" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="46">
+        <v>1100</v>
+      </c>
+      <c r="C24" s="46">
+        <v>1100</v>
+      </c>
+      <c r="D24" s="46">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="46">
+        <v>1100</v>
+      </c>
+      <c r="F24" s="41">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="46">
+        <v>2400</v>
+      </c>
+      <c r="C25" s="46">
+        <v>2400</v>
+      </c>
+      <c r="D25" s="46">
+        <v>2400</v>
+      </c>
+      <c r="E25" s="46">
+        <v>2400</v>
+      </c>
+      <c r="F25" s="41">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="46">
+        <v>1945</v>
+      </c>
+      <c r="C26" s="46">
+        <v>1945</v>
+      </c>
+      <c r="D26" s="46">
+        <v>1945</v>
+      </c>
+      <c r="E26" s="46">
+        <v>1945</v>
+      </c>
+      <c r="F26" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="46">
+        <v>2760</v>
+      </c>
+      <c r="C27" s="46">
+        <v>2760</v>
+      </c>
+      <c r="D27" s="46">
+        <v>2760</v>
+      </c>
+      <c r="E27" s="46">
+        <v>2760</v>
+      </c>
+      <c r="F27" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="46">
+        <v>2780</v>
+      </c>
+      <c r="C28" s="46">
+        <v>2780</v>
+      </c>
+      <c r="D28" s="46">
+        <v>2780</v>
+      </c>
+      <c r="E28" s="46">
+        <v>2780</v>
+      </c>
+      <c r="F28" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="46">
+        <v>2450</v>
+      </c>
+      <c r="C29" s="46">
+        <v>2450</v>
+      </c>
+      <c r="D29" s="46">
+        <v>2450</v>
+      </c>
+      <c r="E29" s="46">
+        <v>2450</v>
+      </c>
+      <c r="F29" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="46">
+        <v>2900</v>
+      </c>
+      <c r="C30" s="46">
+        <v>2900</v>
+      </c>
+      <c r="D30" s="46">
+        <v>2900</v>
+      </c>
+      <c r="E30" s="46">
+        <v>2900</v>
+      </c>
+      <c r="F30" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="46">
+        <v>890</v>
+      </c>
+      <c r="C31" s="46">
+        <v>890</v>
+      </c>
+      <c r="D31" s="46">
+        <v>890</v>
+      </c>
+      <c r="E31" s="46">
+        <v>890</v>
+      </c>
+      <c r="F31" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="46">
+        <v>1560</v>
+      </c>
+      <c r="C32" s="46">
+        <v>1560</v>
+      </c>
+      <c r="D32" s="46">
+        <v>1560</v>
+      </c>
+      <c r="E32" s="46">
+        <v>1560</v>
+      </c>
+      <c r="F32" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="46">
+        <v>1790</v>
+      </c>
+      <c r="C33" s="46">
+        <v>1790</v>
+      </c>
+      <c r="D33" s="46">
+        <v>1790</v>
+      </c>
+      <c r="E33" s="46">
+        <v>1790</v>
+      </c>
+      <c r="F33" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="46">
+        <v>1945</v>
+      </c>
+      <c r="C34" s="46">
+        <v>1945</v>
+      </c>
+      <c r="D34" s="46">
+        <v>1945</v>
+      </c>
+      <c r="E34" s="46">
+        <v>1945</v>
+      </c>
+      <c r="F34" s="41">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C35" s="46">
+        <v>2100</v>
+      </c>
+      <c r="D35" s="46">
+        <v>2100</v>
+      </c>
+      <c r="E35" s="46">
+        <v>2100</v>
+      </c>
+      <c r="F35" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="46">
+        <v>896</v>
+      </c>
+      <c r="C36" s="46">
+        <v>896</v>
+      </c>
+      <c r="D36" s="46">
+        <v>896</v>
+      </c>
+      <c r="E36" s="46">
+        <v>896</v>
+      </c>
+      <c r="F36" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="46">
+        <v>2390</v>
+      </c>
+      <c r="C37" s="46">
+        <v>2390</v>
+      </c>
+      <c r="D37" s="46">
+        <v>2390</v>
+      </c>
+      <c r="E37" s="46">
+        <v>2390</v>
+      </c>
+      <c r="F37" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="46">
+        <v>2480</v>
+      </c>
+      <c r="C38" s="46">
+        <v>2480</v>
+      </c>
+      <c r="D38" s="46">
+        <v>2480</v>
+      </c>
+      <c r="E38" s="46">
+        <v>2480</v>
+      </c>
+      <c r="F38" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="46">
+        <v>57578</v>
+      </c>
+      <c r="C39" s="46">
+        <v>2503.391304347826</v>
+      </c>
+      <c r="D39" s="46">
+        <v>4780</v>
+      </c>
+      <c r="E39" s="46">
+        <v>980</v>
+      </c>
+      <c r="F39" s="41">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="46">
+        <v>2500</v>
+      </c>
+      <c r="C40" s="46">
+        <v>2500</v>
+      </c>
+      <c r="D40" s="46">
+        <v>2500</v>
+      </c>
+      <c r="E40" s="46">
+        <v>2500</v>
+      </c>
+      <c r="F40" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="46">
+        <v>2700</v>
+      </c>
+      <c r="C41" s="46">
+        <v>2700</v>
+      </c>
+      <c r="D41" s="46">
+        <v>2700</v>
+      </c>
+      <c r="E41" s="46">
+        <v>2700</v>
+      </c>
+      <c r="F41" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="46">
+        <v>2790</v>
+      </c>
+      <c r="C42" s="46">
+        <v>2790</v>
+      </c>
+      <c r="D42" s="46">
+        <v>2790</v>
+      </c>
+      <c r="E42" s="46">
+        <v>2790</v>
+      </c>
+      <c r="F42" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="46">
+        <v>4780</v>
+      </c>
+      <c r="C43" s="46">
+        <v>4780</v>
+      </c>
+      <c r="D43" s="46">
+        <v>4780</v>
+      </c>
+      <c r="E43" s="46">
+        <v>4780</v>
+      </c>
+      <c r="F43" s="41">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" s="46">
+        <v>2769</v>
+      </c>
+      <c r="C44" s="46">
+        <v>2769</v>
+      </c>
+      <c r="D44" s="46">
+        <v>2769</v>
+      </c>
+      <c r="E44" s="46">
+        <v>2769</v>
+      </c>
+      <c r="F44" s="41">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="46">
+        <v>3200</v>
+      </c>
+      <c r="C45" s="46">
+        <v>3200</v>
+      </c>
+      <c r="D45" s="46">
+        <v>3200</v>
+      </c>
+      <c r="E45" s="46">
+        <v>3200</v>
+      </c>
+      <c r="F45" s="41">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="46">
+        <v>3190</v>
+      </c>
+      <c r="C46" s="46">
+        <v>3190</v>
+      </c>
+      <c r="D46" s="46">
+        <v>3190</v>
+      </c>
+      <c r="E46" s="46">
+        <v>3190</v>
+      </c>
+      <c r="F46" s="41">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="46">
+        <v>1320</v>
+      </c>
+      <c r="C47" s="46">
+        <v>1320</v>
+      </c>
+      <c r="D47" s="46">
+        <v>1320</v>
+      </c>
+      <c r="E47" s="46">
+        <v>1320</v>
+      </c>
+      <c r="F47" s="41">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C48" s="46">
+        <v>2100</v>
+      </c>
+      <c r="D48" s="46">
+        <v>2100</v>
+      </c>
+      <c r="E48" s="46">
+        <v>2100</v>
+      </c>
+      <c r="F48" s="41">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="46">
+        <v>2640</v>
+      </c>
+      <c r="C49" s="46">
+        <v>2640</v>
+      </c>
+      <c r="D49" s="46">
+        <v>2640</v>
+      </c>
+      <c r="E49" s="46">
+        <v>2640</v>
+      </c>
+      <c r="F49" s="41">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="46">
+        <v>2000</v>
+      </c>
+      <c r="C50" s="46">
+        <v>2000</v>
+      </c>
+      <c r="D50" s="46">
+        <v>2000</v>
+      </c>
+      <c r="E50" s="46">
+        <v>2000</v>
+      </c>
+      <c r="F50" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="46">
+        <v>3010</v>
+      </c>
+      <c r="C51" s="46">
+        <v>3010</v>
+      </c>
+      <c r="D51" s="46">
+        <v>3010</v>
+      </c>
+      <c r="E51" s="46">
+        <v>3010</v>
+      </c>
+      <c r="F51" s="41">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" s="46">
+        <v>2000</v>
+      </c>
+      <c r="C52" s="46">
+        <v>2000</v>
+      </c>
+      <c r="D52" s="46">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="46">
+        <v>2000</v>
+      </c>
+      <c r="F52" s="41">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" s="46">
+        <v>2980</v>
+      </c>
+      <c r="C53" s="46">
+        <v>2980</v>
+      </c>
+      <c r="D53" s="46">
+        <v>2980</v>
+      </c>
+      <c r="E53" s="46">
+        <v>2980</v>
+      </c>
+      <c r="F53" s="41">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="46">
+        <v>980</v>
+      </c>
+      <c r="C54" s="46">
+        <v>980</v>
+      </c>
+      <c r="D54" s="46">
+        <v>980</v>
+      </c>
+      <c r="E54" s="46">
+        <v>980</v>
+      </c>
+      <c r="F54" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="45" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" s="46">
+        <v>3000</v>
+      </c>
+      <c r="C55" s="46">
+        <v>3000</v>
+      </c>
+      <c r="D55" s="46">
+        <v>3000</v>
+      </c>
+      <c r="E55" s="46">
+        <v>3000</v>
+      </c>
+      <c r="F55" s="41">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" s="46">
+        <v>2560</v>
+      </c>
+      <c r="C56" s="46">
+        <v>2560</v>
+      </c>
+      <c r="D56" s="46">
+        <v>2560</v>
+      </c>
+      <c r="E56" s="46">
+        <v>2560</v>
+      </c>
+      <c r="F56" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" s="46">
+        <v>2850</v>
+      </c>
+      <c r="C57" s="46">
+        <v>2850</v>
+      </c>
+      <c r="D57" s="46">
+        <v>2850</v>
+      </c>
+      <c r="E57" s="46">
+        <v>2850</v>
+      </c>
+      <c r="F57" s="41">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C58" s="46">
+        <v>2100</v>
+      </c>
+      <c r="D58" s="46">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="46">
+        <v>2100</v>
+      </c>
+      <c r="F58" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="46">
+        <v>2109</v>
+      </c>
+      <c r="C59" s="46">
+        <v>2109</v>
+      </c>
+      <c r="D59" s="46">
+        <v>2109</v>
+      </c>
+      <c r="E59" s="46">
+        <v>2109</v>
+      </c>
+      <c r="F59" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="46">
+        <v>2900</v>
+      </c>
+      <c r="C60" s="46">
+        <v>2900</v>
+      </c>
+      <c r="D60" s="46">
+        <v>2900</v>
+      </c>
+      <c r="E60" s="46">
+        <v>2900</v>
+      </c>
+      <c r="F60" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C61" s="46">
+        <v>2100</v>
+      </c>
+      <c r="D61" s="46">
+        <v>2100</v>
+      </c>
+      <c r="E61" s="46">
+        <v>2100</v>
+      </c>
+      <c r="F61" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" s="46">
+        <v>1000</v>
+      </c>
+      <c r="C62" s="46">
+        <v>1000</v>
+      </c>
+      <c r="D62" s="46">
+        <v>1000</v>
+      </c>
+      <c r="E62" s="46">
+        <v>1000</v>
+      </c>
+      <c r="F62" s="41">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B63" s="46">
+        <v>44585</v>
+      </c>
+      <c r="C63" s="46">
+        <v>2123.0952380952381</v>
+      </c>
+      <c r="D63" s="46">
+        <v>4500</v>
+      </c>
+      <c r="E63" s="46">
+        <v>950</v>
+      </c>
+      <c r="F63" s="41">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="46">
+        <v>1800</v>
+      </c>
+      <c r="C64" s="46">
+        <v>1800</v>
+      </c>
+      <c r="D64" s="46">
+        <v>1800</v>
+      </c>
+      <c r="E64" s="46">
+        <v>1800</v>
+      </c>
+      <c r="F64" s="41">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B65" s="46">
+        <v>1750</v>
+      </c>
+      <c r="C65" s="46">
+        <v>1750</v>
+      </c>
+      <c r="D65" s="46">
+        <v>1750</v>
+      </c>
+      <c r="E65" s="46">
+        <v>1750</v>
+      </c>
+      <c r="F65" s="41">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" s="46">
+        <v>2000</v>
+      </c>
+      <c r="C66" s="46">
+        <v>2000</v>
+      </c>
+      <c r="D66" s="46">
+        <v>2000</v>
+      </c>
+      <c r="E66" s="46">
+        <v>2000</v>
+      </c>
+      <c r="F66" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B67" s="46">
+        <v>3500</v>
+      </c>
+      <c r="C67" s="46">
+        <v>3500</v>
+      </c>
+      <c r="D67" s="46">
+        <v>3500</v>
+      </c>
+      <c r="E67" s="46">
+        <v>3500</v>
+      </c>
+      <c r="F67" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B68" s="46">
+        <v>4500</v>
+      </c>
+      <c r="C68" s="46">
+        <v>4500</v>
+      </c>
+      <c r="D68" s="46">
+        <v>4500</v>
+      </c>
+      <c r="E68" s="46">
+        <v>4500</v>
+      </c>
+      <c r="F68" s="41">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="46">
+        <v>1450</v>
+      </c>
+      <c r="C69" s="46">
+        <v>1450</v>
+      </c>
+      <c r="D69" s="46">
+        <v>1450</v>
+      </c>
+      <c r="E69" s="46">
+        <v>1450</v>
+      </c>
+      <c r="F69" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="46">
+        <v>3600</v>
+      </c>
+      <c r="C70" s="46">
+        <v>3600</v>
+      </c>
+      <c r="D70" s="46">
+        <v>3600</v>
+      </c>
+      <c r="E70" s="46">
+        <v>3600</v>
+      </c>
+      <c r="F70" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B71" s="46">
+        <v>1600</v>
+      </c>
+      <c r="C71" s="46">
+        <v>1600</v>
+      </c>
+      <c r="D71" s="46">
+        <v>1600</v>
+      </c>
+      <c r="E71" s="46">
+        <v>1600</v>
+      </c>
+      <c r="F71" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" s="46">
+        <v>3200</v>
+      </c>
+      <c r="C72" s="46">
+        <v>3200</v>
+      </c>
+      <c r="D72" s="46">
+        <v>3200</v>
+      </c>
+      <c r="E72" s="46">
+        <v>3200</v>
+      </c>
+      <c r="F72" s="41">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B73" s="46">
+        <v>2850</v>
+      </c>
+      <c r="C73" s="46">
+        <v>2850</v>
+      </c>
+      <c r="D73" s="46">
+        <v>2850</v>
+      </c>
+      <c r="E73" s="46">
+        <v>2850</v>
+      </c>
+      <c r="F73" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" s="46">
+        <v>1050</v>
+      </c>
+      <c r="C74" s="46">
+        <v>1050</v>
+      </c>
+      <c r="D74" s="46">
+        <v>1050</v>
+      </c>
+      <c r="E74" s="46">
+        <v>1050</v>
+      </c>
+      <c r="F74" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B75" s="46">
+        <v>1320</v>
+      </c>
+      <c r="C75" s="46">
+        <v>1320</v>
+      </c>
+      <c r="D75" s="46">
+        <v>1320</v>
+      </c>
+      <c r="E75" s="46">
+        <v>1320</v>
+      </c>
+      <c r="F75" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B76" s="46">
+        <v>1020</v>
+      </c>
+      <c r="C76" s="46">
+        <v>1020</v>
+      </c>
+      <c r="D76" s="46">
+        <v>1020</v>
+      </c>
+      <c r="E76" s="46">
+        <v>1020</v>
+      </c>
+      <c r="F76" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B77" s="46">
+        <v>2890</v>
+      </c>
+      <c r="C77" s="46">
+        <v>2890</v>
+      </c>
+      <c r="D77" s="46">
+        <v>2890</v>
+      </c>
+      <c r="E77" s="46">
+        <v>2890</v>
+      </c>
+      <c r="F77" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="46">
+        <v>950</v>
+      </c>
+      <c r="C78" s="46">
+        <v>950</v>
+      </c>
+      <c r="D78" s="46">
+        <v>950</v>
+      </c>
+      <c r="E78" s="46">
+        <v>950</v>
+      </c>
+      <c r="F78" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="B79" s="46">
+        <v>990</v>
+      </c>
+      <c r="C79" s="46">
+        <v>990</v>
+      </c>
+      <c r="D79" s="46">
+        <v>990</v>
+      </c>
+      <c r="E79" s="46">
+        <v>990</v>
+      </c>
+      <c r="F79" s="41">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="46">
+        <v>1000</v>
+      </c>
+      <c r="C80" s="46">
+        <v>1000</v>
+      </c>
+      <c r="D80" s="46">
+        <v>1000</v>
+      </c>
+      <c r="E80" s="46">
+        <v>1000</v>
+      </c>
+      <c r="F80" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B81" s="46">
+        <v>1035</v>
+      </c>
+      <c r="C81" s="46">
+        <v>1035</v>
+      </c>
+      <c r="D81" s="46">
+        <v>1035</v>
+      </c>
+      <c r="E81" s="46">
+        <v>1035</v>
+      </c>
+      <c r="F81" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82" s="46">
+        <v>3100</v>
+      </c>
+      <c r="C82" s="46">
+        <v>3100</v>
+      </c>
+      <c r="D82" s="46">
+        <v>3100</v>
+      </c>
+      <c r="E82" s="46">
+        <v>3100</v>
+      </c>
+      <c r="F82" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="46">
+        <v>3000</v>
+      </c>
+      <c r="C83" s="46">
+        <v>3000</v>
+      </c>
+      <c r="D83" s="46">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="46">
+        <v>3000</v>
+      </c>
+      <c r="F83" s="41">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84" s="46">
+        <v>1980</v>
+      </c>
+      <c r="C84" s="46">
+        <v>1980</v>
+      </c>
+      <c r="D84" s="46">
+        <v>1980</v>
+      </c>
+      <c r="E84" s="46">
+        <v>1980</v>
+      </c>
+      <c r="F84" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B85" s="46">
+        <v>56315</v>
+      </c>
+      <c r="C85" s="46">
+        <v>2346.4583333333335</v>
+      </c>
+      <c r="D85" s="46">
+        <v>4200</v>
+      </c>
+      <c r="E85" s="46">
+        <v>956</v>
+      </c>
+      <c r="F85" s="41">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B86" s="46">
+        <v>2300</v>
+      </c>
+      <c r="C86" s="46">
+        <v>2300</v>
+      </c>
+      <c r="D86" s="46">
+        <v>2300</v>
+      </c>
+      <c r="E86" s="46">
+        <v>2300</v>
+      </c>
+      <c r="F86" s="41">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C87" s="46">
+        <v>2100</v>
+      </c>
+      <c r="D87" s="46">
+        <v>2100</v>
+      </c>
+      <c r="E87" s="46">
+        <v>2100</v>
+      </c>
+      <c r="F87" s="41">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88" s="46">
+        <v>2470</v>
+      </c>
+      <c r="C88" s="46">
+        <v>2470</v>
+      </c>
+      <c r="D88" s="46">
+        <v>2470</v>
+      </c>
+      <c r="E88" s="46">
+        <v>2470</v>
+      </c>
+      <c r="F88" s="41">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B89" s="46">
+        <v>2700</v>
+      </c>
+      <c r="C89" s="46">
+        <v>2700</v>
+      </c>
+      <c r="D89" s="46">
+        <v>2700</v>
+      </c>
+      <c r="E89" s="46">
+        <v>2700</v>
+      </c>
+      <c r="F89" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" s="46">
+        <v>2780</v>
+      </c>
+      <c r="C90" s="46">
+        <v>2780</v>
+      </c>
+      <c r="D90" s="46">
+        <v>2780</v>
+      </c>
+      <c r="E90" s="46">
+        <v>2780</v>
+      </c>
+      <c r="F90" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B91" s="46">
+        <v>3200</v>
+      </c>
+      <c r="C91" s="46">
+        <v>3200</v>
+      </c>
+      <c r="D91" s="46">
+        <v>3200</v>
+      </c>
+      <c r="E91" s="46">
+        <v>3200</v>
+      </c>
+      <c r="F91" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B92" s="46">
+        <v>4200</v>
+      </c>
+      <c r="C92" s="46">
+        <v>4200</v>
+      </c>
+      <c r="D92" s="46">
+        <v>4200</v>
+      </c>
+      <c r="E92" s="46">
+        <v>4200</v>
+      </c>
+      <c r="F92" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B93" s="46">
+        <v>1458</v>
+      </c>
+      <c r="C93" s="46">
+        <v>1458</v>
+      </c>
+      <c r="D93" s="46">
+        <v>1458</v>
+      </c>
+      <c r="E93" s="46">
+        <v>1458</v>
+      </c>
+      <c r="F93" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B94" s="46">
+        <v>1400</v>
+      </c>
+      <c r="C94" s="46">
+        <v>1400</v>
+      </c>
+      <c r="D94" s="46">
+        <v>1400</v>
+      </c>
+      <c r="E94" s="46">
+        <v>1400</v>
+      </c>
+      <c r="F94" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="46">
+        <v>1890</v>
+      </c>
+      <c r="C95" s="46">
+        <v>1890</v>
+      </c>
+      <c r="D95" s="46">
+        <v>1890</v>
+      </c>
+      <c r="E95" s="46">
+        <v>1890</v>
+      </c>
+      <c r="F95" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" s="46">
+        <v>1000</v>
+      </c>
+      <c r="C96" s="46">
+        <v>1000</v>
+      </c>
+      <c r="D96" s="46">
+        <v>1000</v>
+      </c>
+      <c r="E96" s="46">
+        <v>1000</v>
+      </c>
+      <c r="F96" s="41">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B97" s="46">
+        <v>2980</v>
+      </c>
+      <c r="C97" s="46">
+        <v>2980</v>
+      </c>
+      <c r="D97" s="46">
+        <v>2980</v>
+      </c>
+      <c r="E97" s="46">
+        <v>2980</v>
+      </c>
+      <c r="F97" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B98" s="46">
+        <v>3000</v>
+      </c>
+      <c r="C98" s="46">
+        <v>3000</v>
+      </c>
+      <c r="D98" s="46">
+        <v>3000</v>
+      </c>
+      <c r="E98" s="46">
+        <v>3000</v>
+      </c>
+      <c r="F98" s="41">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B99" s="46">
+        <v>2900</v>
+      </c>
+      <c r="C99" s="46">
+        <v>2900</v>
+      </c>
+      <c r="D99" s="46">
+        <v>2900</v>
+      </c>
+      <c r="E99" s="46">
+        <v>2900</v>
+      </c>
+      <c r="F99" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="45" t="s">
+        <v>63</v>
+      </c>
+      <c r="B100" s="46">
+        <v>3100</v>
+      </c>
+      <c r="C100" s="46">
+        <v>3100</v>
+      </c>
+      <c r="D100" s="46">
+        <v>3100</v>
+      </c>
+      <c r="E100" s="46">
+        <v>3100</v>
+      </c>
+      <c r="F100" s="41">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="B101" s="46">
+        <v>2950</v>
+      </c>
+      <c r="C101" s="46">
+        <v>2950</v>
+      </c>
+      <c r="D101" s="46">
+        <v>2950</v>
+      </c>
+      <c r="E101" s="46">
+        <v>2950</v>
+      </c>
+      <c r="F101" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B102" s="46">
+        <v>3050</v>
+      </c>
+      <c r="C102" s="46">
+        <v>3050</v>
+      </c>
+      <c r="D102" s="46">
+        <v>3050</v>
+      </c>
+      <c r="E102" s="46">
+        <v>3050</v>
+      </c>
+      <c r="F102" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B103" s="46">
+        <v>956</v>
+      </c>
+      <c r="C103" s="46">
+        <v>956</v>
+      </c>
+      <c r="D103" s="46">
+        <v>956</v>
+      </c>
+      <c r="E103" s="46">
+        <v>956</v>
+      </c>
+      <c r="F103" s="41">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="B104" s="46">
+        <v>1060</v>
+      </c>
+      <c r="C104" s="46">
+        <v>1060</v>
+      </c>
+      <c r="D104" s="46">
+        <v>1060</v>
+      </c>
+      <c r="E104" s="46">
+        <v>1060</v>
+      </c>
+      <c r="F104" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B105" s="46">
+        <v>2764</v>
+      </c>
+      <c r="C105" s="46">
+        <v>2764</v>
+      </c>
+      <c r="D105" s="46">
+        <v>2764</v>
+      </c>
+      <c r="E105" s="46">
+        <v>2764</v>
+      </c>
+      <c r="F105" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="B106" s="46">
+        <v>2740</v>
+      </c>
+      <c r="C106" s="46">
+        <v>2740</v>
+      </c>
+      <c r="D106" s="46">
+        <v>2740</v>
+      </c>
+      <c r="E106" s="46">
+        <v>2740</v>
+      </c>
+      <c r="F106" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B107" s="46">
+        <v>1090</v>
+      </c>
+      <c r="C107" s="46">
+        <v>1090</v>
+      </c>
+      <c r="D107" s="46">
+        <v>1090</v>
+      </c>
+      <c r="E107" s="46">
+        <v>1090</v>
+      </c>
+      <c r="F107" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B108" s="46">
+        <v>3120</v>
+      </c>
+      <c r="C108" s="46">
+        <v>3120</v>
+      </c>
+      <c r="D108" s="46">
+        <v>3120</v>
+      </c>
+      <c r="E108" s="46">
+        <v>3120</v>
+      </c>
+      <c r="F108" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B109" s="46">
+        <v>1107</v>
+      </c>
+      <c r="C109" s="46">
+        <v>1107</v>
+      </c>
+      <c r="D109" s="46">
+        <v>1107</v>
+      </c>
+      <c r="E109" s="46">
+        <v>1107</v>
+      </c>
+      <c r="F109" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="B110" s="46">
+        <v>225369</v>
+      </c>
+      <c r="C110" s="46">
+        <v>2209.5</v>
+      </c>
+      <c r="D110" s="46">
+        <v>4780</v>
+      </c>
+      <c r="E110" s="46">
+        <v>890</v>
+      </c>
+      <c r="F110" s="41">
+        <v>4598</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751232CB-99D3-4E21-BA24-439A0890EF51}">
+  <dimension ref="A2:C111"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="29" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="37" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="17" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="18" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="16" bestFit="1" customWidth="1"/>
+    <col min="59" max="60" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="21" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="21" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="16" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="12" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="16" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="46">
+        <v>66891</v>
+      </c>
+      <c r="C5" s="41">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="46">
+        <v>1250</v>
+      </c>
+      <c r="C6" s="41">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="46">
+        <v>4000</v>
+      </c>
+      <c r="C7" s="41">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="46">
+        <v>1678</v>
+      </c>
+      <c r="C8" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="46">
+        <v>1200</v>
+      </c>
+      <c r="C9" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="46">
+        <v>1207</v>
+      </c>
+      <c r="C10" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="46">
+        <v>1560</v>
+      </c>
+      <c r="C11" s="41">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="46">
+        <v>1564</v>
+      </c>
+      <c r="C12" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="46">
+        <v>1800</v>
+      </c>
+      <c r="C13" s="41">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="46">
+        <v>2180</v>
+      </c>
+      <c r="C14" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="46">
+        <v>2570</v>
+      </c>
+      <c r="C15" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="46">
+        <v>2650</v>
+      </c>
+      <c r="C16" s="41">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="46">
+        <v>2176</v>
+      </c>
+      <c r="C17" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C18" s="41">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C19" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="46">
+        <v>1250</v>
+      </c>
+      <c r="C20" s="41">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="46">
+        <v>1100</v>
+      </c>
+      <c r="C21" s="41">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="46">
+        <v>2040</v>
+      </c>
+      <c r="C22" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C23" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="46">
+        <v>1980</v>
+      </c>
+      <c r="C24" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="46">
+        <v>1100</v>
+      </c>
+      <c r="C25" s="41">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="46">
+        <v>2400</v>
+      </c>
+      <c r="C26" s="41">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="46">
+        <v>1945</v>
+      </c>
+      <c r="C27" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="46">
+        <v>2760</v>
+      </c>
+      <c r="C28" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="46">
+        <v>2780</v>
+      </c>
+      <c r="C29" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="46">
+        <v>2450</v>
+      </c>
+      <c r="C30" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="46">
+        <v>2900</v>
+      </c>
+      <c r="C31" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="46">
+        <v>890</v>
+      </c>
+      <c r="C32" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="46">
+        <v>1560</v>
+      </c>
+      <c r="C33" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="46">
+        <v>1790</v>
+      </c>
+      <c r="C34" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="46">
+        <v>1945</v>
+      </c>
+      <c r="C35" s="41">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C36" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="46">
+        <v>896</v>
+      </c>
+      <c r="C37" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="46">
+        <v>2390</v>
+      </c>
+      <c r="C38" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="46">
+        <v>2480</v>
+      </c>
+      <c r="C39" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="46">
+        <v>57578</v>
+      </c>
+      <c r="C40" s="41">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="46">
+        <v>2500</v>
+      </c>
+      <c r="C41" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="46">
+        <v>2700</v>
+      </c>
+      <c r="C42" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" s="46">
+        <v>2790</v>
+      </c>
+      <c r="C43" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="46">
+        <v>4780</v>
+      </c>
+      <c r="C44" s="41">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="46">
+        <v>2769</v>
+      </c>
+      <c r="C45" s="41">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="46">
+        <v>3200</v>
+      </c>
+      <c r="C46" s="41">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="46">
+        <v>3190</v>
+      </c>
+      <c r="C47" s="41">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="46">
+        <v>1320</v>
+      </c>
+      <c r="C48" s="41">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C49" s="41">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="46">
+        <v>2640</v>
+      </c>
+      <c r="C50" s="41">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="46">
+        <v>2000</v>
+      </c>
+      <c r="C51" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="46">
+        <v>3010</v>
+      </c>
+      <c r="C52" s="41">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="46">
+        <v>2000</v>
+      </c>
+      <c r="C53" s="41">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" s="46">
+        <v>2980</v>
+      </c>
+      <c r="C54" s="41">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="46">
+        <v>980</v>
+      </c>
+      <c r="C55" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="45" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="46">
+        <v>3000</v>
+      </c>
+      <c r="C56" s="41">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B57" s="46">
+        <v>2560</v>
+      </c>
+      <c r="C57" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="46">
+        <v>2850</v>
+      </c>
+      <c r="C58" s="41">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C59" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="46">
+        <v>2109</v>
+      </c>
+      <c r="C60" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="46">
+        <v>2900</v>
+      </c>
+      <c r="C61" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C62" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" s="46">
+        <v>1000</v>
+      </c>
+      <c r="C63" s="41">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" s="46">
+        <v>44585</v>
+      </c>
+      <c r="C64" s="41">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="46">
+        <v>1800</v>
+      </c>
+      <c r="C65" s="41">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66" s="46">
+        <v>1750</v>
+      </c>
+      <c r="C66" s="41">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" s="46">
+        <v>2000</v>
+      </c>
+      <c r="C67" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" s="46">
+        <v>3500</v>
+      </c>
+      <c r="C68" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" s="46">
+        <v>4500</v>
+      </c>
+      <c r="C69" s="41">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70" s="46">
+        <v>1450</v>
+      </c>
+      <c r="C70" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="46">
+        <v>3600</v>
+      </c>
+      <c r="C71" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" s="46">
+        <v>1600</v>
+      </c>
+      <c r="C72" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="46">
+        <v>3200</v>
+      </c>
+      <c r="C73" s="41">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B74" s="46">
+        <v>2850</v>
+      </c>
+      <c r="C74" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" s="46">
+        <v>1050</v>
+      </c>
+      <c r="C75" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" s="46">
+        <v>1320</v>
+      </c>
+      <c r="C76" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77" s="46">
+        <v>1020</v>
+      </c>
+      <c r="C77" s="41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B78" s="46">
+        <v>2890</v>
+      </c>
+      <c r="C78" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="46">
+        <v>950</v>
+      </c>
+      <c r="C79" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="B80" s="46">
+        <v>990</v>
+      </c>
+      <c r="C80" s="41">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B81" s="46">
+        <v>1000</v>
+      </c>
+      <c r="C81" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B82" s="46">
+        <v>1035</v>
+      </c>
+      <c r="C82" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="B83" s="46">
+        <v>3100</v>
+      </c>
+      <c r="C83" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="46">
+        <v>3000</v>
+      </c>
+      <c r="C84" s="41">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85" s="46">
+        <v>1980</v>
+      </c>
+      <c r="C85" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" s="46">
+        <v>56315</v>
+      </c>
+      <c r="C86" s="41">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B87" s="46">
+        <v>2300</v>
+      </c>
+      <c r="C87" s="41">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B88" s="46">
+        <v>2100</v>
+      </c>
+      <c r="C88" s="41">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="B89" s="46">
+        <v>2470</v>
+      </c>
+      <c r="C89" s="41">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B90" s="46">
+        <v>2700</v>
+      </c>
+      <c r="C90" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B91" s="46">
+        <v>2780</v>
+      </c>
+      <c r="C91" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B92" s="46">
+        <v>3200</v>
+      </c>
+      <c r="C92" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B93" s="46">
+        <v>4200</v>
+      </c>
+      <c r="C93" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B94" s="46">
+        <v>1458</v>
+      </c>
+      <c r="C94" s="41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B95" s="46">
+        <v>1400</v>
+      </c>
+      <c r="C95" s="41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="46">
+        <v>1890</v>
+      </c>
+      <c r="C96" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B97" s="46">
+        <v>1000</v>
+      </c>
+      <c r="C97" s="41">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B98" s="46">
+        <v>2980</v>
+      </c>
+      <c r="C98" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B99" s="46">
+        <v>3000</v>
+      </c>
+      <c r="C99" s="41">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B100" s="46">
+        <v>2900</v>
+      </c>
+      <c r="C100" s="41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="45" t="s">
+        <v>63</v>
+      </c>
+      <c r="B101" s="46">
+        <v>3100</v>
+      </c>
+      <c r="C101" s="41">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" s="46">
+        <v>2950</v>
+      </c>
+      <c r="C102" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103" s="46">
+        <v>3050</v>
+      </c>
+      <c r="C103" s="41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B104" s="46">
+        <v>956</v>
+      </c>
+      <c r="C104" s="41">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="B105" s="46">
+        <v>1060</v>
+      </c>
+      <c r="C105" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B106" s="46">
+        <v>2764</v>
+      </c>
+      <c r="C106" s="41">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="B107" s="46">
+        <v>2740</v>
+      </c>
+      <c r="C107" s="41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B108" s="46">
+        <v>1090</v>
+      </c>
+      <c r="C108" s="41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B109" s="46">
+        <v>3120</v>
+      </c>
+      <c r="C109" s="41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B110" s="46">
+        <v>1107</v>
+      </c>
+      <c r="C110" s="41">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="B111" s="46">
+        <v>225369</v>
+      </c>
+      <c r="C111" s="41">
+        <v>4598</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" style="6" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" style="7" customWidth="1"/>
     <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="11" max="11" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="53.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -1066,11 +7242,11 @@
       <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>82</v>
       </c>
@@ -1086,39 +7262,39 @@
       <c r="E3" s="2">
         <v>33605</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="15">
         <f ca="1">INT((TODAY()-E3)/365.25)</f>
         <v>34</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="16">
         <f ca="1">DATEDIF(E3,TODAY(),"Y")</f>
         <v>34</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>94</v>
+      <c r="K3" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D4" s="5">
-        <v>2500</v>
+        <v>1250</v>
       </c>
       <c r="E4" s="2">
-        <v>31940</v>
-      </c>
-      <c r="F4" s="18">
-        <f t="shared" ref="F4:F67" ca="1" si="0">INT((TODAY()-E4)/365.25)</f>
-        <v>39</v>
-      </c>
-      <c r="K4" s="22" t="s">
+        <v>33501</v>
+      </c>
+      <c r="F4" s="13">
+        <f ca="1">INT((TODAY()-E4)/365.25)</f>
+        <v>35</v>
+      </c>
+      <c r="K4" s="23" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1138,29 +7314,29 @@
       <c r="E5" s="2">
         <v>28623</v>
       </c>
-      <c r="F5" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F5" s="13">
+        <f ca="1">INT((TODAY()-E5)/365.25)</f>
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D6" s="5">
-        <v>1250</v>
+        <v>1560</v>
       </c>
       <c r="E6" s="2">
-        <v>33501</v>
-      </c>
-      <c r="F6" s="18">
-        <f t="shared" ca="1" si="0"/>
+        <v>33199</v>
+      </c>
+      <c r="F6" s="13">
+        <f ca="1">INT((TODAY()-E6)/365.25)</f>
         <v>35</v>
       </c>
     </row>
@@ -1175,13 +7351,13 @@
         <v>112</v>
       </c>
       <c r="D7" s="5">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="E7" s="2">
         <v>24027</v>
       </c>
-      <c r="F7" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F7" s="13">
+        <f ca="1">INT((TODAY()-E7)/365.25)</f>
         <v>60</v>
       </c>
     </row>
@@ -1201,8 +7377,8 @@
       <c r="E8" s="2">
         <v>32827</v>
       </c>
-      <c r="F8" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F8" s="13">
+        <f ca="1">INT((TODAY()-E8)/365.25)</f>
         <v>36</v>
       </c>
     </row>
@@ -1222,8 +7398,8 @@
       <c r="E9" s="2">
         <v>28302</v>
       </c>
-      <c r="F9" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F9" s="13">
+        <f ca="1">INT((TODAY()-E9)/365.25)</f>
         <v>49</v>
       </c>
     </row>
@@ -1243,8 +7419,8 @@
       <c r="E10" s="2">
         <v>24209</v>
       </c>
-      <c r="F10" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F10" s="13">
+        <f ca="1">INT((TODAY()-E10)/365.25)</f>
         <v>60</v>
       </c>
     </row>
@@ -1264,8 +7440,8 @@
       <c r="E11" s="2">
         <v>24531</v>
       </c>
-      <c r="F11" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F11" s="13">
+        <f ca="1">INT((TODAY()-E11)/365.25)</f>
         <v>59</v>
       </c>
     </row>
@@ -1285,8 +7461,8 @@
       <c r="E12" s="2">
         <v>30759</v>
       </c>
-      <c r="F12" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F12" s="13">
+        <f ca="1">INT((TODAY()-E12)/365.25)</f>
         <v>42</v>
       </c>
     </row>
@@ -1306,8 +7482,8 @@
       <c r="E13" s="2">
         <v>33053</v>
       </c>
-      <c r="F13" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F13" s="13">
+        <f ca="1">INT((TODAY()-E13)/365.25)</f>
         <v>36</v>
       </c>
     </row>
@@ -1327,8 +7503,8 @@
       <c r="E14" s="2">
         <v>31258</v>
       </c>
-      <c r="F14" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F14" s="13">
+        <f ca="1">INT((TODAY()-E14)/365.25)</f>
         <v>41</v>
       </c>
     </row>
@@ -1348,8 +7524,8 @@
       <c r="E15" s="2">
         <v>30905</v>
       </c>
-      <c r="F15" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F15" s="13">
+        <f ca="1">INT((TODAY()-E15)/365.25)</f>
         <v>42</v>
       </c>
     </row>
@@ -1369,8 +7545,8 @@
       <c r="E16" s="2">
         <v>28867</v>
       </c>
-      <c r="F16" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F16" s="13">
+        <f ca="1">INT((TODAY()-E16)/365.25)</f>
         <v>47</v>
       </c>
     </row>
@@ -1390,8 +7566,8 @@
       <c r="E17" s="2">
         <v>29265</v>
       </c>
-      <c r="F17" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F17" s="13">
+        <f ca="1">INT((TODAY()-E17)/365.25)</f>
         <v>46</v>
       </c>
     </row>
@@ -1411,30 +7587,30 @@
       <c r="E18" s="2">
         <v>21681</v>
       </c>
-      <c r="F18" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F18" s="13">
+        <f ca="1">INT((TODAY()-E18)/365.25)</f>
         <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D19" s="5">
-        <v>1200</v>
+        <v>2640</v>
       </c>
       <c r="E19" s="2">
-        <v>32006</v>
-      </c>
-      <c r="F19" s="18">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>33505</v>
+      </c>
+      <c r="F19" s="13">
+        <f ca="1">INT((TODAY()-E19)/365.25)</f>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1453,8 +7629,8 @@
       <c r="E20" s="2">
         <v>32493</v>
       </c>
-      <c r="F20" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F20" s="13">
+        <f ca="1">INT((TODAY()-E20)/365.25)</f>
         <v>37</v>
       </c>
     </row>
@@ -1474,8 +7650,8 @@
       <c r="E21" s="2">
         <v>21936</v>
       </c>
-      <c r="F21" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F21" s="13">
+        <f ca="1">INT((TODAY()-E21)/365.25)</f>
         <v>66</v>
       </c>
     </row>
@@ -1495,8 +7671,8 @@
       <c r="E22" s="2">
         <v>32947</v>
       </c>
-      <c r="F22" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F22" s="13">
+        <f ca="1">INT((TODAY()-E22)/365.25)</f>
         <v>36</v>
       </c>
     </row>
@@ -1516,8 +7692,8 @@
       <c r="E23" s="2">
         <v>31072</v>
       </c>
-      <c r="F23" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F23" s="13">
+        <f ca="1">INT((TODAY()-E23)/365.25)</f>
         <v>41</v>
       </c>
     </row>
@@ -1537,14 +7713,14 @@
       <c r="E24" s="2">
         <v>24958</v>
       </c>
-      <c r="F24" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F24" s="13">
+        <f ca="1">INT((TODAY()-E24)/365.25)</f>
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>9</v>
+      <c r="A25" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>108</v>
@@ -1553,14 +7729,14 @@
         <v>113</v>
       </c>
       <c r="D25" s="5">
-        <v>1560</v>
+        <v>1200</v>
       </c>
       <c r="E25" s="2">
-        <v>33199</v>
-      </c>
-      <c r="F25" s="18">
-        <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>32006</v>
+      </c>
+      <c r="F25" s="13">
+        <f ca="1">INT((TODAY()-E25)/365.25)</f>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1579,8 +7755,8 @@
       <c r="E26" s="2">
         <v>28777</v>
       </c>
-      <c r="F26" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F26" s="13">
+        <f ca="1">INT((TODAY()-E26)/365.25)</f>
         <v>47</v>
       </c>
     </row>
@@ -1600,8 +7776,8 @@
       <c r="E27" s="2">
         <v>28029</v>
       </c>
-      <c r="F27" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F27" s="13">
+        <f ca="1">INT((TODAY()-E27)/365.25)</f>
         <v>50</v>
       </c>
     </row>
@@ -1621,8 +7797,8 @@
       <c r="E28" s="2">
         <v>32640</v>
       </c>
-      <c r="F28" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F28" s="13">
+        <f ca="1">INT((TODAY()-E28)/365.25)</f>
         <v>37</v>
       </c>
     </row>
@@ -1642,8 +7818,8 @@
       <c r="E29" s="2">
         <v>29022</v>
       </c>
-      <c r="F29" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F29" s="13">
+        <f ca="1">INT((TODAY()-E29)/365.25)</f>
         <v>47</v>
       </c>
     </row>
@@ -1663,8 +7839,8 @@
       <c r="E30" s="2">
         <v>22235</v>
       </c>
-      <c r="F30" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F30" s="13">
+        <f ca="1">INT((TODAY()-E30)/365.25)</f>
         <v>65</v>
       </c>
     </row>
@@ -1684,8 +7860,8 @@
       <c r="E31" s="2">
         <v>30406</v>
       </c>
-      <c r="F31" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F31" s="13">
+        <f ca="1">INT((TODAY()-E31)/365.25)</f>
         <v>43</v>
       </c>
     </row>
@@ -1705,8 +7881,8 @@
       <c r="E32" s="2">
         <v>30136</v>
       </c>
-      <c r="F32" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F32" s="13">
+        <f ca="1">INT((TODAY()-E32)/365.25)</f>
         <v>44</v>
       </c>
     </row>
@@ -1726,8 +7902,8 @@
       <c r="E33" s="2">
         <v>31412</v>
       </c>
-      <c r="F33" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F33" s="13">
+        <f ca="1">INT((TODAY()-E33)/365.25)</f>
         <v>40</v>
       </c>
     </row>
@@ -1747,8 +7923,8 @@
       <c r="E34" s="2">
         <v>29530</v>
       </c>
-      <c r="F34" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F34" s="13">
+        <f ca="1">INT((TODAY()-E34)/365.25)</f>
         <v>45</v>
       </c>
     </row>
@@ -1768,8 +7944,8 @@
       <c r="E35" s="2">
         <v>30776</v>
       </c>
-      <c r="F35" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F35" s="13">
+        <f ca="1">INT((TODAY()-E35)/365.25)</f>
         <v>42</v>
       </c>
     </row>
@@ -1789,29 +7965,29 @@
       <c r="E36" s="2">
         <v>28756</v>
       </c>
-      <c r="F36" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F36" s="13">
+        <f ca="1">INT((TODAY()-E36)/365.25)</f>
         <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D37" s="5">
-        <v>1600</v>
+        <v>2390</v>
       </c>
       <c r="E37" s="2">
-        <v>31707</v>
-      </c>
-      <c r="F37" s="18">
-        <f t="shared" ca="1" si="0"/>
+        <v>31753</v>
+      </c>
+      <c r="F37" s="13">
+        <f ca="1">INT((TODAY()-E37)/365.25)</f>
         <v>39</v>
       </c>
     </row>
@@ -1831,8 +8007,8 @@
       <c r="E38" s="2">
         <v>24635</v>
       </c>
-      <c r="F38" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F38" s="13">
+        <f ca="1">INT((TODAY()-E38)/365.25)</f>
         <v>59</v>
       </c>
     </row>
@@ -1852,8 +8028,8 @@
       <c r="E39" s="2">
         <v>20714</v>
       </c>
-      <c r="F39" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F39" s="13">
+        <f ca="1">INT((TODAY()-E39)/365.25)</f>
         <v>70</v>
       </c>
     </row>
@@ -1873,8 +8049,8 @@
       <c r="E40" s="2">
         <v>29738</v>
       </c>
-      <c r="F40" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F40" s="13">
+        <f ca="1">INT((TODAY()-E40)/365.25)</f>
         <v>45</v>
       </c>
     </row>
@@ -1894,8 +8070,8 @@
       <c r="E41" s="2">
         <v>24762</v>
       </c>
-      <c r="F41" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F41" s="13">
+        <f ca="1">INT((TODAY()-E41)/365.25)</f>
         <v>58</v>
       </c>
     </row>
@@ -1915,8 +8091,8 @@
       <c r="E42" s="2">
         <v>29504</v>
       </c>
-      <c r="F42" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F42" s="13">
+        <f ca="1">INT((TODAY()-E42)/365.25)</f>
         <v>45</v>
       </c>
     </row>
@@ -1936,8 +8112,8 @@
       <c r="E43" s="2">
         <v>33018</v>
       </c>
-      <c r="F43" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F43" s="13">
+        <f ca="1">INT((TODAY()-E43)/365.25)</f>
         <v>36</v>
       </c>
     </row>
@@ -1957,29 +8133,29 @@
       <c r="E44" s="2">
         <v>30279</v>
       </c>
-      <c r="F44" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F44" s="13">
+        <f ca="1">INT((TODAY()-E44)/365.25)</f>
         <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>13</v>
+      <c r="A45" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D45" s="5">
-        <v>1320</v>
+        <v>2500</v>
       </c>
       <c r="E45" s="2">
-        <v>31756</v>
-      </c>
-      <c r="F45" s="18">
-        <f t="shared" ca="1" si="0"/>
+        <v>31940</v>
+      </c>
+      <c r="F45" s="13">
+        <f ca="1">INT((TODAY()-E45)/365.25)</f>
         <v>39</v>
       </c>
     </row>
@@ -1999,14 +8175,14 @@
       <c r="E46" s="2">
         <v>28207</v>
       </c>
-      <c r="F46" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F46" s="13">
+        <f ca="1">INT((TODAY()-E46)/365.25)</f>
         <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>95</v>
+      <c r="A47" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>107</v>
@@ -2015,14 +8191,14 @@
         <v>111</v>
       </c>
       <c r="D47" s="5">
-        <v>2640</v>
+        <v>2900</v>
       </c>
       <c r="E47" s="2">
-        <v>33505</v>
-      </c>
-      <c r="F47" s="18">
-        <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>31900</v>
+      </c>
+      <c r="F47" s="13">
+        <f ca="1">INT((TODAY()-E47)/365.25)</f>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2041,8 +8217,8 @@
       <c r="E48" s="2">
         <v>27166</v>
       </c>
-      <c r="F48" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F48" s="13">
+        <f ca="1">INT((TODAY()-E48)/365.25)</f>
         <v>52</v>
       </c>
     </row>
@@ -2062,8 +8238,8 @@
       <c r="E49" s="2">
         <v>32948</v>
       </c>
-      <c r="F49" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F49" s="13">
+        <f ca="1">INT((TODAY()-E49)/365.25)</f>
         <v>36</v>
       </c>
     </row>
@@ -2083,8 +8259,8 @@
       <c r="E50" s="2">
         <v>30289</v>
       </c>
-      <c r="F50" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F50" s="13">
+        <f ca="1">INT((TODAY()-E50)/365.25)</f>
         <v>43</v>
       </c>
     </row>
@@ -2104,8 +8280,8 @@
       <c r="E51" s="2">
         <v>32442</v>
       </c>
-      <c r="F51" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F51" s="13">
+        <f ca="1">INT((TODAY()-E51)/365.25)</f>
         <v>37</v>
       </c>
     </row>
@@ -2125,8 +8301,8 @@
       <c r="E52" s="2">
         <v>25308</v>
       </c>
-      <c r="F52" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F52" s="13">
+        <f ca="1">INT((TODAY()-E52)/365.25)</f>
         <v>57</v>
       </c>
     </row>
@@ -2146,8 +8322,8 @@
       <c r="E53" s="2">
         <v>32391</v>
       </c>
-      <c r="F53" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F53" s="13">
+        <f ca="1">INT((TODAY()-E53)/365.25)</f>
         <v>38</v>
       </c>
     </row>
@@ -2167,8 +8343,8 @@
       <c r="E54" s="2">
         <v>28215</v>
       </c>
-      <c r="F54" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F54" s="13">
+        <f ca="1">INT((TODAY()-E54)/365.25)</f>
         <v>49</v>
       </c>
     </row>
@@ -2188,8 +8364,8 @@
       <c r="E55" s="2">
         <v>28708</v>
       </c>
-      <c r="F55" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F55" s="13">
+        <f ca="1">INT((TODAY()-E55)/365.25)</f>
         <v>48</v>
       </c>
     </row>
@@ -2209,14 +8385,14 @@
       <c r="E56" s="2">
         <v>29771</v>
       </c>
-      <c r="F56" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F56" s="13">
+        <f ca="1">INT((TODAY()-E56)/365.25)</f>
         <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>109</v>
@@ -2225,14 +8401,14 @@
         <v>113</v>
       </c>
       <c r="D57" s="5">
-        <v>1020</v>
+        <v>1600</v>
       </c>
       <c r="E57" s="2">
-        <v>32052</v>
-      </c>
-      <c r="F57" s="18">
-        <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>31707</v>
+      </c>
+      <c r="F57" s="13">
+        <f ca="1">INT((TODAY()-E57)/365.25)</f>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2251,8 +8427,8 @@
       <c r="E58" s="2">
         <v>30662</v>
       </c>
-      <c r="F58" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F58" s="13">
+        <f ca="1">INT((TODAY()-E58)/365.25)</f>
         <v>42</v>
       </c>
     </row>
@@ -2272,8 +8448,8 @@
       <c r="E59" s="2">
         <v>29782</v>
       </c>
-      <c r="F59" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F59" s="13">
+        <f ca="1">INT((TODAY()-E59)/365.25)</f>
         <v>45</v>
       </c>
     </row>
@@ -2293,8 +8469,8 @@
       <c r="E60" s="2">
         <v>28161</v>
       </c>
-      <c r="F60" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F60" s="13">
+        <f ca="1">INT((TODAY()-E60)/365.25)</f>
         <v>49</v>
       </c>
     </row>
@@ -2314,8 +8490,8 @@
       <c r="E61" s="2">
         <v>30994</v>
       </c>
-      <c r="F61" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F61" s="13">
+        <f ca="1">INT((TODAY()-E61)/365.25)</f>
         <v>41</v>
       </c>
     </row>
@@ -2335,8 +8511,8 @@
       <c r="E62" s="2">
         <v>32273</v>
       </c>
-      <c r="F62" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F62" s="13">
+        <f ca="1">INT((TODAY()-E62)/365.25)</f>
         <v>38</v>
       </c>
     </row>
@@ -2356,8 +8532,8 @@
       <c r="E63" s="2">
         <v>24882</v>
       </c>
-      <c r="F63" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F63" s="13">
+        <f ca="1">INT((TODAY()-E63)/365.25)</f>
         <v>58</v>
       </c>
     </row>
@@ -2377,8 +8553,8 @@
       <c r="E64" s="2">
         <v>30953</v>
       </c>
-      <c r="F64" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F64" s="13">
+        <f ca="1">INT((TODAY()-E64)/365.25)</f>
         <v>42</v>
       </c>
     </row>
@@ -2398,8 +8574,8 @@
       <c r="E65" s="2">
         <v>27017</v>
       </c>
-      <c r="F65" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F65" s="13">
+        <f ca="1">INT((TODAY()-E65)/365.25)</f>
         <v>52</v>
       </c>
     </row>
@@ -2419,8 +8595,8 @@
       <c r="E66" s="2">
         <v>29486</v>
       </c>
-      <c r="F66" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F66" s="13">
+        <f ca="1">INT((TODAY()-E66)/365.25)</f>
         <v>46</v>
       </c>
     </row>
@@ -2440,8 +8616,8 @@
       <c r="E67" s="2">
         <v>25402</v>
       </c>
-      <c r="F67" s="18">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F67" s="13">
+        <f ca="1">INT((TODAY()-E67)/365.25)</f>
         <v>57</v>
       </c>
     </row>
@@ -2461,8 +8637,8 @@
       <c r="E68" s="2">
         <v>30458</v>
       </c>
-      <c r="F68" s="18">
-        <f t="shared" ref="F68:F104" ca="1" si="1">INT((TODAY()-E68)/365.25)</f>
+      <c r="F68" s="13">
+        <f ca="1">INT((TODAY()-E68)/365.25)</f>
         <v>43</v>
       </c>
     </row>
@@ -2482,8 +8658,8 @@
       <c r="E69" s="2">
         <v>29221</v>
       </c>
-      <c r="F69" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F69" s="13">
+        <f ca="1">INT((TODAY()-E69)/365.25)</f>
         <v>46</v>
       </c>
     </row>
@@ -2503,8 +8679,8 @@
       <c r="E70" s="2">
         <v>30240</v>
       </c>
-      <c r="F70" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F70" s="13">
+        <f ca="1">INT((TODAY()-E70)/365.25)</f>
         <v>43</v>
       </c>
     </row>
@@ -2524,8 +8700,8 @@
       <c r="E71" s="2">
         <v>32363</v>
       </c>
-      <c r="F71" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F71" s="13">
+        <f ca="1">INT((TODAY()-E71)/365.25)</f>
         <v>38</v>
       </c>
     </row>
@@ -2545,8 +8721,8 @@
       <c r="E72" s="2">
         <v>30943</v>
       </c>
-      <c r="F72" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F72" s="13">
+        <f ca="1">INT((TODAY()-E72)/365.25)</f>
         <v>42</v>
       </c>
     </row>
@@ -2566,8 +8742,8 @@
       <c r="E73" s="2">
         <v>27144</v>
       </c>
-      <c r="F73" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F73" s="13">
+        <f ca="1">INT((TODAY()-E73)/365.25)</f>
         <v>52</v>
       </c>
     </row>
@@ -2587,8 +8763,8 @@
       <c r="E74" s="2">
         <v>25086</v>
       </c>
-      <c r="F74" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F74" s="13">
+        <f ca="1">INT((TODAY()-E74)/365.25)</f>
         <v>58</v>
       </c>
     </row>
@@ -2608,8 +8784,8 @@
       <c r="E75" s="2">
         <v>32832</v>
       </c>
-      <c r="F75" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F75" s="13">
+        <f ca="1">INT((TODAY()-E75)/365.25)</f>
         <v>36</v>
       </c>
     </row>
@@ -2629,8 +8805,8 @@
       <c r="E76" s="2">
         <v>29033</v>
       </c>
-      <c r="F76" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F76" s="13">
+        <f ca="1">INT((TODAY()-E76)/365.25)</f>
         <v>47</v>
       </c>
     </row>
@@ -2650,8 +8826,8 @@
       <c r="E77" s="2">
         <v>30584</v>
       </c>
-      <c r="F77" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F77" s="13">
+        <f ca="1">INT((TODAY()-E77)/365.25)</f>
         <v>43</v>
       </c>
     </row>
@@ -2671,8 +8847,8 @@
       <c r="E78" s="2">
         <v>25857</v>
       </c>
-      <c r="F78" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F78" s="13">
+        <f ca="1">INT((TODAY()-E78)/365.25)</f>
         <v>55</v>
       </c>
     </row>
@@ -2692,8 +8868,8 @@
       <c r="E79" s="2">
         <v>32514</v>
       </c>
-      <c r="F79" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F79" s="13">
+        <f ca="1">INT((TODAY()-E79)/365.25)</f>
         <v>37</v>
       </c>
     </row>
@@ -2713,8 +8889,8 @@
       <c r="E80" s="2">
         <v>29540</v>
       </c>
-      <c r="F80" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F80" s="13">
+        <f ca="1">INT((TODAY()-E80)/365.25)</f>
         <v>45</v>
       </c>
     </row>
@@ -2734,8 +8910,8 @@
       <c r="E81" s="2">
         <v>29194</v>
       </c>
-      <c r="F81" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F81" s="13">
+        <f ca="1">INT((TODAY()-E81)/365.25)</f>
         <v>46</v>
       </c>
     </row>
@@ -2755,8 +8931,8 @@
       <c r="E82" s="2">
         <v>30378</v>
       </c>
-      <c r="F82" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F82" s="13">
+        <f ca="1">INT((TODAY()-E82)/365.25)</f>
         <v>43</v>
       </c>
     </row>
@@ -2776,8 +8952,8 @@
       <c r="E83" s="2">
         <v>28826</v>
       </c>
-      <c r="F83" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F83" s="13">
+        <f ca="1">INT((TODAY()-E83)/365.25)</f>
         <v>47</v>
       </c>
     </row>
@@ -2797,8 +8973,8 @@
       <c r="E84" s="2">
         <v>32703</v>
       </c>
-      <c r="F84" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F84" s="13">
+        <f ca="1">INT((TODAY()-E84)/365.25)</f>
         <v>37</v>
       </c>
     </row>
@@ -2818,8 +8994,8 @@
       <c r="E85" s="2">
         <v>29369</v>
       </c>
-      <c r="F85" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F85" s="13">
+        <f ca="1">INT((TODAY()-E85)/365.25)</f>
         <v>46</v>
       </c>
     </row>
@@ -2839,9 +9015,9 @@
       <c r="E86" s="2">
         <v>32783</v>
       </c>
-      <c r="F86" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+      <c r="F86" s="13">
+        <f ca="1">INT((TODAY()-E86)/365.25)</f>
+        <v>37</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2860,8 +9036,8 @@
       <c r="E87" s="2">
         <v>31067</v>
       </c>
-      <c r="F87" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F87" s="13">
+        <f ca="1">INT((TODAY()-E87)/365.25)</f>
         <v>41</v>
       </c>
     </row>
@@ -2881,8 +9057,8 @@
       <c r="E88" s="2">
         <v>31109</v>
       </c>
-      <c r="F88" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F88" s="13">
+        <f ca="1">INT((TODAY()-E88)/365.25)</f>
         <v>41</v>
       </c>
     </row>
@@ -2902,9 +9078,9 @@
       <c r="E89" s="2">
         <v>28767</v>
       </c>
-      <c r="F89" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>47</v>
+      <c r="F89" s="13">
+        <f ca="1">INT((TODAY()-E89)/365.25)</f>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2923,8 +9099,8 @@
       <c r="E90" s="2">
         <v>32803</v>
       </c>
-      <c r="F90" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F90" s="13">
+        <f ca="1">INT((TODAY()-E90)/365.25)</f>
         <v>36</v>
       </c>
     </row>
@@ -2944,8 +9120,8 @@
       <c r="E91" s="2">
         <v>31192</v>
       </c>
-      <c r="F91" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F91" s="13">
+        <f ca="1">INT((TODAY()-E91)/365.25)</f>
         <v>41</v>
       </c>
     </row>
@@ -2965,29 +9141,29 @@
       <c r="E92" s="2">
         <v>29789</v>
       </c>
-      <c r="F92" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F92" s="13">
+        <f ca="1">INT((TODAY()-E92)/365.25)</f>
         <v>45</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D93" s="5">
-        <v>2900</v>
+        <v>1320</v>
       </c>
       <c r="E93" s="2">
-        <v>31900</v>
-      </c>
-      <c r="F93" s="18">
-        <f t="shared" ca="1" si="1"/>
+        <v>31756</v>
+      </c>
+      <c r="F93" s="13">
+        <f ca="1">INT((TODAY()-E93)/365.25)</f>
         <v>39</v>
       </c>
     </row>
@@ -3007,8 +9183,8 @@
       <c r="E94" s="2">
         <v>30267</v>
       </c>
-      <c r="F94" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F94" s="13">
+        <f ca="1">INT((TODAY()-E94)/365.25)</f>
         <v>43</v>
       </c>
     </row>
@@ -3028,8 +9204,8 @@
       <c r="E95" s="2">
         <v>31212</v>
       </c>
-      <c r="F95" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F95" s="13">
+        <f ca="1">INT((TODAY()-E95)/365.25)</f>
         <v>41</v>
       </c>
     </row>
@@ -3049,8 +9225,8 @@
       <c r="E96" s="2">
         <v>32721</v>
       </c>
-      <c r="F96" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F96" s="13">
+        <f ca="1">INT((TODAY()-E96)/365.25)</f>
         <v>37</v>
       </c>
     </row>
@@ -3070,8 +9246,8 @@
       <c r="E97" s="2">
         <v>30806</v>
       </c>
-      <c r="F97" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F97" s="13">
+        <f ca="1">INT((TODAY()-E97)/365.25)</f>
         <v>42</v>
       </c>
     </row>
@@ -3091,8 +9267,8 @@
       <c r="E98" s="2">
         <v>25117</v>
       </c>
-      <c r="F98" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F98" s="13">
+        <f ca="1">INT((TODAY()-E98)/365.25)</f>
         <v>57</v>
       </c>
     </row>
@@ -3112,8 +9288,8 @@
       <c r="E99" s="2">
         <v>32749</v>
       </c>
-      <c r="F99" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F99" s="13">
+        <f ca="1">INT((TODAY()-E99)/365.25)</f>
         <v>37</v>
       </c>
     </row>
@@ -3133,8 +9309,8 @@
       <c r="E100" s="2">
         <v>27487</v>
       </c>
-      <c r="F100" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F100" s="13">
+        <f ca="1">INT((TODAY()-E100)/365.25)</f>
         <v>51</v>
       </c>
     </row>
@@ -3154,8 +9330,8 @@
       <c r="E101" s="2">
         <v>30405</v>
       </c>
-      <c r="F101" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F101" s="13">
+        <f ca="1">INT((TODAY()-E101)/365.25)</f>
         <v>43</v>
       </c>
     </row>
@@ -3175,29 +9351,29 @@
       <c r="E102" s="2">
         <v>28914</v>
       </c>
-      <c r="F102" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F102" s="13">
+        <f ca="1">INT((TODAY()-E102)/365.25)</f>
         <v>47</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D103" s="5">
-        <v>2390</v>
+        <v>1020</v>
       </c>
       <c r="E103" s="2">
-        <v>31753</v>
-      </c>
-      <c r="F103" s="18">
-        <f t="shared" ca="1" si="1"/>
+        <v>32052</v>
+      </c>
+      <c r="F103" s="13">
+        <f ca="1">INT((TODAY()-E103)/365.25)</f>
         <v>39</v>
       </c>
     </row>
@@ -3217,8 +9393,8 @@
       <c r="E104" s="2">
         <v>32835</v>
       </c>
-      <c r="F104" s="18">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F104" s="13">
+        <f t="shared" ref="F68:F104" ca="1" si="0">INT((TODAY()-E104)/365.25)</f>
         <v>36</v>
       </c>
     </row>
@@ -3234,7 +9410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3251,24 +9427,24 @@
     <col min="10" max="10" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="49.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38"/>
     </row>
     <row r="2" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -3307,39 +9483,63 @@
       <c r="L2" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="O2" s="26" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O2" s="19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="20">
         <f>DSUM(DADOS,salario,ADM)</f>
-        <v>66391</v>
-      </c>
-      <c r="C3" s="5">
+        <v>66891</v>
+      </c>
+      <c r="C3" s="24">
         <f>DAVERAGE(DADOS,salario,ADM)</f>
-        <v>1952.6764705882354</v>
-      </c>
-      <c r="D3" s="5">
+        <v>1967.3823529411766</v>
+      </c>
+      <c r="D3" s="25">
         <f>DMAX(DADOS,salario,ADM)</f>
-        <v>3500</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="4"/>
-      <c r="O3" s="27" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4000</v>
+      </c>
+      <c r="E3" s="33" t="str">
+        <f>DGET(DADOS,funcionario,adm_max_sal)</f>
+        <v>Ana Cristina Paiva</v>
+      </c>
+      <c r="F3" s="26">
+        <f>DMIN(DADOS,salario,ADM)</f>
+        <v>890</v>
+      </c>
+      <c r="G3" s="34" t="str">
+        <f>DGET(DADOS,funcionario,adm_min_sal)</f>
+        <v>Rogerio Dias</v>
+      </c>
+      <c r="H3" s="27">
+        <f>DCOUNT(DADOS,salario,ADM)</f>
+        <v>34</v>
+      </c>
+      <c r="I3" s="12">
+        <f ca="1">DMAX(DADOS,idade,ADM)</f>
+        <v>60</v>
+      </c>
+      <c r="J3" s="4" t="str">
+        <f ca="1">DGET(DADOS,funcionario,adm_max_idd)</f>
+        <v>Ana Cristina Paiva</v>
+      </c>
+      <c r="K3" s="12">
+        <f ca="1">DMIN(DADOS,idade,ADM)</f>
+        <v>35</v>
+      </c>
+      <c r="L3" s="4" t="e">
+        <f ca="1">DGET(DADOS,funcionario,adm_min_idd)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>107</v>
       </c>
@@ -3355,16 +9555,43 @@
         <f>DMAX(DADOS,salario,FIN)</f>
         <v>4780</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E4" s="33" t="str">
+        <f>DGET(DADOS,funcionario,fin_max_sal)</f>
+        <v>Fernanda Marioni</v>
+      </c>
+      <c r="F4" s="5">
+        <f>DMIN(DADOS,salario,FIN)</f>
+        <v>980</v>
+      </c>
+      <c r="G4" s="34" t="str">
+        <f>DGET(DADOS,funcionario,fin_min_sal)</f>
+        <v>Maria do Carmo Leal</v>
+      </c>
+      <c r="H4" s="12">
+        <f>DCOUNT(DADOS,salario,FIN)</f>
+        <v>23</v>
+      </c>
+      <c r="I4" s="12">
+        <f ca="1">DMAX(DADOS,idade,FIN)</f>
+        <v>70</v>
+      </c>
+      <c r="J4" s="4" t="str">
+        <f ca="1">DGET(DADOS,funcionario,fin_max_idd)</f>
+        <v>Jaciara Yonh</v>
+      </c>
+      <c r="K4" s="12">
+        <f ca="1">DMIN(DADOS,idade,FIN)</f>
+        <v>35</v>
+      </c>
+      <c r="L4" s="4" t="str">
+        <f ca="1">DGET(DADOS,funcionario,fin_min_idd)</f>
+        <v>Jussara Medeiros</v>
+      </c>
+      <c r="O4" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>109</v>
       </c>
@@ -3380,16 +9607,43 @@
         <f>DMAX(DADOS,salario,INF)</f>
         <v>4500</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E5" s="33" t="str">
+        <f>DGET(DADOS,funcionario,inf_max_sal)</f>
+        <v>Diógenes Duarte Lima</v>
+      </c>
+      <c r="F5" s="5">
+        <f>DMIN(DADOS,salario,INF)</f>
+        <v>950</v>
+      </c>
+      <c r="G5" s="34" t="str">
+        <f>DGET(DADOS,funcionario,inf_min_sal)</f>
+        <v>Maria Inês Fagundes</v>
+      </c>
+      <c r="H5" s="12">
+        <f>DCOUNT(DADOS,salario,INF)</f>
+        <v>21</v>
+      </c>
+      <c r="I5" s="12">
+        <f ca="1">DMAX(DADOS,idade,INF)</f>
+        <v>67</v>
+      </c>
+      <c r="J5" s="4" t="str">
+        <f ca="1">DGET(DADOS,funcionario,inf_max_idd)</f>
+        <v>Diógenes Duarte Lima</v>
+      </c>
+      <c r="K5" s="12">
+        <f ca="1">DMIN(DADOS,idade,INF)</f>
+        <v>39</v>
+      </c>
+      <c r="L5" s="4" t="e">
+        <f ca="1">DGET(DADOS,funcionario,inf_min_idd)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O5" s="29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>106</v>
       </c>
@@ -3405,33 +9659,71 @@
         <f>DMAX(DADOS,salario,RH)</f>
         <v>4200</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E6" s="33" t="str">
+        <f>DGET(DADOS,funcionario,rh_max_sal)</f>
+        <v>Georgina Nythe</v>
+      </c>
+      <c r="F6" s="5">
+        <f>DMIN(DADOS,salario,RH)</f>
+        <v>956</v>
+      </c>
+      <c r="G6" s="34" t="str">
+        <f>DGET(DADOS,funcionario,rh_min_sal)</f>
+        <v>Marineide Novais</v>
+      </c>
+      <c r="H6" s="12">
+        <f>DCOUNT(DADOS,salario,RH)</f>
+        <v>24</v>
+      </c>
+      <c r="I6" s="12">
+        <f ca="1">DMAX(DADOS,idade,RH)</f>
+        <v>59</v>
+      </c>
+      <c r="J6" s="4" t="str">
+        <f ca="1">DGET(DADOS,funcionario,rh_max_idd)</f>
+        <v>Barbara Hioli</v>
+      </c>
+      <c r="K6" s="12">
+        <f ca="1">DMIN(DADOS,idade,RH)</f>
+        <v>34</v>
+      </c>
+      <c r="L6" s="4" t="str">
+        <f ca="1">DGET(DADOS,funcionario,rh_min_idd)</f>
+        <v>Alan Golden</v>
+      </c>
+      <c r="O6" s="30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E7" s="6"/>
+      <c r="O7" s="31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="O8" s="22" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="9" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="17"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="38"/>
+      <c r="O9" s="42" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="10" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
@@ -3475,7 +9767,10 @@
       <c r="A11" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="5">
+        <f>DSUM(DADOS,cargo,analista)</f>
+        <v>0</v>
+      </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="4"/>
@@ -3561,59 +9856,498 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="41" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="M1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="B2" s="32">
+        <f>RELATÓRIO!D3</f>
+        <v>4000</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="32">
+        <f>RELATÓRIO!F3</f>
+        <v>890</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="40">
+        <f ca="1">RELATÓRIO!I3</f>
+        <v>60</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="40">
+        <f ca="1">RELATÓRIO!K3</f>
+        <v>35</v>
+      </c>
+      <c r="O2" s="17" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="25" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="L3" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="32">
+        <f>RELATÓRIO!D4</f>
+        <v>4780</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="32">
+        <f>RELATÓRIO!F4</f>
+        <v>980</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="40">
+        <f ca="1">RELATÓRIO!I4</f>
+        <v>70</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="L4" s="40">
+        <f ca="1">RELATÓRIO!K4</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="I5" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="32">
+        <f>RELATÓRIO!D5</f>
+        <v>4500</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="32">
+        <f>RELATÓRIO!F5</f>
+        <v>950</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I6" s="40">
+        <f ca="1">RELATÓRIO!I5</f>
+        <v>67</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="L6" s="40">
+        <f ca="1">RELATÓRIO!K5</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="L7" s="39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>106</v>
+      </c>
+      <c r="B8" s="32">
+        <f>RELATÓRIO!D6</f>
+        <v>4200</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="32">
+        <f>RELATÓRIO!F6</f>
+        <v>956</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="40">
+        <f ca="1">RELATÓRIO!I6</f>
+        <v>59</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L8" s="40">
+        <f ca="1">RELATÓRIO!K6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="J10" t="s">
+        <v>139</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="M10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="32">
+        <f>RELATÓRIO!D12</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="32">
+        <f>RELATÓRIO!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="32">
+        <f>RELATÓRIO!K12</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="L11" s="32">
+        <f>RELATÓRIO!N12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="32">
+        <f>RELATÓRIO!D13</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="32">
+        <f>RELATÓRIO!G13</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="32">
+        <f>RELATÓRIO!K13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="32">
+        <f>RELATÓRIO!N13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="32">
+        <f>RELATÓRIO!D14</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="32">
+        <f>RELATÓRIO!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="32">
+        <f>RELATÓRIO!K14</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L15" s="32">
+        <f>RELATÓRIO!N14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="32">
+        <f>RELATÓRIO!D15</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="32">
+        <f>RELATÓRIO!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I17" s="32">
+        <f>RELATÓRIO!K15</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17" s="32">
+        <f>RELATÓRIO!N15</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +10356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9044851-4546-4A88-91D0-002C6DA394F8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3632,6 +10366,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3640,7 +10380,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -3754,13 +10494,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7634936-3474-4A47-A34B-4DDC3BAA309F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AEBB415-50F8-461A-8B46-9D41A0BDDBAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3768,7 +10511,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25CCED7B-9E3C-4A46-87C8-9A405AC9C3A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3782,13 +10525,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7634936-3474-4A47-A34B-4DDC3BAA309F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>